--- a/output/2025/EFISIENSI PER DINAS.xlsx
+++ b/output/2025/EFISIENSI PER DINAS.xlsx
@@ -2275,19 +2275,19 @@
         <v>405807500</v>
       </c>
       <c r="FR4" s="4">
-        <v>460007000</v>
+        <v>617348000</v>
       </c>
       <c r="FS4" s="4">
-        <v>54199500</v>
+        <v>211540500</v>
       </c>
       <c r="FT4" s="4">
-        <v>86.64403688941185</v>
+        <v>47.8717125730796</v>
       </c>
       <c r="FU4" s="4">
         <v>31698000</v>
       </c>
       <c r="FV4" s="4">
-        <v>351608000</v>
+        <v>194267000</v>
       </c>
       <c r="FW4" s="4">
         <v>160098000</v>
@@ -2299,19 +2299,19 @@
         <v>80049000</v>
       </c>
       <c r="FZ4" s="4">
-        <v>61163000</v>
+        <v>83559000</v>
       </c>
       <c r="GA4" s="4">
-        <v>-18886000</v>
+        <v>3510000</v>
       </c>
       <c r="GB4" s="4">
-        <v>123.59304925732988</v>
+        <v>95.6151856987595</v>
       </c>
       <c r="GC4" s="4">
         <v>17967000</v>
       </c>
       <c r="GD4" s="4">
-        <v>98935000</v>
+        <v>76539000</v>
       </c>
       <c r="GE4" s="4">
         <v>2143600000</v>
@@ -2323,19 +2323,19 @@
         <v>1071800000</v>
       </c>
       <c r="GH4" s="4">
-        <v>1170850000</v>
+        <v>1161700000</v>
       </c>
       <c r="GI4" s="4">
-        <v>99050000</v>
+        <v>89900000</v>
       </c>
       <c r="GJ4" s="4">
-        <v>90.75853704049263</v>
+        <v>91.61224108975556</v>
       </c>
       <c r="GK4" s="4">
         <v>207161000</v>
       </c>
       <c r="GL4" s="4">
-        <v>972750000</v>
+        <v>981900000</v>
       </c>
       <c r="GU4" s="4">
         <v>51111000</v>
@@ -2347,19 +2347,19 @@
         <v>25555500</v>
       </c>
       <c r="GX4" s="4">
-        <v>0</v>
+        <v>28341000</v>
       </c>
       <c r="GY4" s="4">
-        <v>-25555500</v>
+        <v>2785500</v>
       </c>
       <c r="GZ4" s="4">
-        <v>200</v>
+        <v>89.10019369607325</v>
       </c>
       <c r="HA4" s="4">
         <v>0</v>
       </c>
       <c r="HB4" s="4">
-        <v>51111000</v>
+        <v>22770000</v>
       </c>
       <c r="HK4" s="4">
         <v>119140400</v>
@@ -2371,19 +2371,19 @@
         <v>77441260</v>
       </c>
       <c r="HN4" s="4">
-        <v>72400400</v>
+        <v>76073100</v>
       </c>
       <c r="HO4" s="4">
-        <v>-5040860</v>
+        <v>-1368160</v>
       </c>
       <c r="HP4" s="4">
-        <v>112.08864259550677</v>
+        <v>103.28102689887608</v>
       </c>
       <c r="HQ4" s="4">
         <v>23750600</v>
       </c>
       <c r="HR4" s="4">
-        <v>46740000</v>
+        <v>43067300</v>
       </c>
       <c r="HS4" s="4">
         <v>29096200</v>
@@ -2395,19 +2395,19 @@
         <v>18912530</v>
       </c>
       <c r="HV4" s="4">
-        <v>14128500</v>
+        <v>14538600</v>
       </c>
       <c r="HW4" s="4">
-        <v>-4784030</v>
+        <v>-4373930</v>
       </c>
       <c r="HX4" s="4">
-        <v>146.97746490214234</v>
+        <v>142.95042946207016</v>
       </c>
       <c r="HY4" s="4">
         <v>6090000</v>
       </c>
       <c r="HZ4" s="4">
-        <v>14967700</v>
+        <v>14557600</v>
       </c>
       <c r="II4" s="4">
         <v>230530000</v>
@@ -2443,19 +2443,19 @@
         <v>492778000</v>
       </c>
       <c r="IT4" s="4">
-        <v>543580000</v>
+        <v>554380000</v>
       </c>
       <c r="IU4" s="4">
-        <v>50802000</v>
+        <v>61602000</v>
       </c>
       <c r="IV4" s="4">
-        <v>80.85414295512962</v>
+        <v>76.78392414318125</v>
       </c>
       <c r="IW4" s="4">
         <v>77220000</v>
       </c>
       <c r="IX4" s="4">
-        <v>214540000</v>
+        <v>203740000</v>
       </c>
       <c r="JG4" s="4">
         <v>31054970600</v>
@@ -2467,10 +2467,10 @@
         <v>31054970600</v>
       </c>
       <c r="JJ4" s="4">
-        <v>30919680700</v>
+        <v>36908932700</v>
       </c>
       <c r="JK4" s="4">
-        <v>-135289900</v>
+        <v>5853962100</v>
       </c>
       <c r="JL4" s="4">
         <v>0</v>
@@ -2479,7 +2479,7 @@
         <v>45856137793</v>
       </c>
       <c r="JN4" s="4">
-        <v>135289900</v>
+        <v>-5853962100</v>
       </c>
       <c r="JO4" s="4">
         <v>45733281200</v>
@@ -2491,19 +2491,19 @@
         <v>40639658890</v>
       </c>
       <c r="JR4" s="4">
-        <v>40546809600</v>
+        <v>47080089400</v>
       </c>
       <c r="JS4" s="4">
-        <v>-92849290</v>
+        <v>6440430510</v>
       </c>
       <c r="JT4" s="4">
-        <v>101.82285384249465</v>
+        <v>-26.44106920444205</v>
       </c>
       <c r="JU4" s="4">
         <v>2563886600</v>
       </c>
       <c r="JV4" s="4">
-        <v>5186471600</v>
+        <v>-1346808200</v>
       </c>
       <c r="JW4" s="4">
         <v>922385000</v>
@@ -2515,19 +2515,19 @@
         <v>461192500</v>
       </c>
       <c r="JZ4" s="4">
-        <v>523340000</v>
+        <v>680681000</v>
       </c>
       <c r="KA4" s="4">
-        <v>62147500</v>
+        <v>219488500</v>
       </c>
       <c r="KB4" s="4">
-        <v>86.52460740363297</v>
+        <v>52.408484526526344</v>
       </c>
       <c r="KC4" s="4">
         <v>31698000</v>
       </c>
       <c r="KD4" s="4">
-        <v>399045000</v>
+        <v>241704000</v>
       </c>
       <c r="KE4" s="4">
         <v>160098000</v>
@@ -2539,19 +2539,19 @@
         <v>80049000</v>
       </c>
       <c r="KH4" s="4">
-        <v>61163000</v>
+        <v>83559000</v>
       </c>
       <c r="KI4" s="4">
-        <v>-18886000</v>
+        <v>3510000</v>
       </c>
       <c r="KJ4" s="4">
-        <v>123.59304925732988</v>
+        <v>95.6151856987595</v>
       </c>
       <c r="KK4" s="4">
         <v>17967000</v>
       </c>
       <c r="KL4" s="4">
-        <v>98935000</v>
+        <v>76539000</v>
       </c>
       <c r="KM4" s="4">
         <v>2143600000</v>
@@ -2563,19 +2563,19 @@
         <v>1071800000</v>
       </c>
       <c r="KP4" s="4">
-        <v>1170850000</v>
+        <v>1161700000</v>
       </c>
       <c r="KQ4" s="4">
-        <v>99050000</v>
+        <v>89900000</v>
       </c>
       <c r="KR4" s="4">
-        <v>90.75853704049263</v>
+        <v>91.61224108975556</v>
       </c>
       <c r="KS4" s="4">
         <v>207161000</v>
       </c>
       <c r="KT4" s="4">
-        <v>972750000</v>
+        <v>981900000</v>
       </c>
       <c r="LC4" s="4">
         <v>51111000</v>
@@ -2587,19 +2587,19 @@
         <v>25555500</v>
       </c>
       <c r="LF4" s="4">
-        <v>0</v>
+        <v>28341000</v>
       </c>
       <c r="LG4" s="4">
-        <v>-25555500</v>
+        <v>2785500</v>
       </c>
       <c r="LH4" s="4">
-        <v>200</v>
+        <v>89.10019369607325</v>
       </c>
       <c r="LI4" s="4">
         <v>0</v>
       </c>
       <c r="LJ4" s="4">
-        <v>51111000</v>
+        <v>22770000</v>
       </c>
       <c r="LS4" s="4">
         <v>145483200</v>
@@ -2611,19 +2611,19 @@
         <v>94564080</v>
       </c>
       <c r="LV4" s="4">
-        <v>89522400</v>
+        <v>93195100</v>
       </c>
       <c r="LW4" s="4">
-        <v>-5041680</v>
+        <v>-1368980</v>
       </c>
       <c r="LX4" s="4">
-        <v>109.90134943416147</v>
+        <v>102.68853821511448</v>
       </c>
       <c r="LY4" s="4">
         <v>23750600</v>
       </c>
       <c r="LZ4" s="4">
-        <v>55960800</v>
+        <v>52288100</v>
       </c>
       <c r="MA4" s="4">
         <v>42064700</v>
@@ -2635,19 +2635,19 @@
         <v>27342055</v>
       </c>
       <c r="MD4" s="4">
-        <v>22508500</v>
+        <v>22918600</v>
       </c>
       <c r="ME4" s="4">
-        <v>-4833555</v>
+        <v>-4423455</v>
       </c>
       <c r="MF4" s="4">
-        <v>132.83075153955016</v>
+        <v>130.04524662518185</v>
       </c>
       <c r="MG4" s="4">
         <v>6090000</v>
       </c>
       <c r="MH4" s="4">
-        <v>19556200</v>
+        <v>19146100</v>
       </c>
       <c r="MY4" s="4">
         <v>230530000</v>
@@ -2683,19 +2683,19 @@
         <v>492778000</v>
       </c>
       <c r="NR4" s="4">
-        <v>543580000</v>
+        <v>554380000</v>
       </c>
       <c r="NS4" s="4">
-        <v>50802000</v>
+        <v>61602000</v>
       </c>
       <c r="NT4" s="4">
-        <v>80.85414295512962</v>
+        <v>76.78392414318125</v>
       </c>
       <c r="NU4" s="4">
         <v>77220000</v>
       </c>
       <c r="NV4" s="4">
-        <v>214540000</v>
+        <v>203740000</v>
       </c>
       <c r="PS4" s="4">
         <v>10375000000</v>
@@ -2707,19 +2707,19 @@
         <v>7262500000</v>
       </c>
       <c r="PV4" s="4">
-        <v>7305000000</v>
+        <v>7635217000</v>
       </c>
       <c r="PW4" s="4">
-        <v>42500000</v>
+        <v>372717000</v>
       </c>
       <c r="PX4" s="4">
-        <v>98.63453815261045</v>
+        <v>88.02515662650603</v>
       </c>
       <c r="PY4" s="4">
         <v>2200000000</v>
       </c>
       <c r="PZ4" s="4">
-        <v>3070000000</v>
+        <v>2739783000</v>
       </c>
       <c r="QA4" s="4">
         <v>161739594856</v>
@@ -2731,10 +2731,10 @@
         <v>161739594856</v>
       </c>
       <c r="QD4" s="4">
-        <v>161212982556</v>
+        <v>167006457556</v>
       </c>
       <c r="QE4" s="4">
-        <v>-526612300</v>
+        <v>5266862700</v>
       </c>
       <c r="QF4" s="4">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>59347086558</v>
       </c>
       <c r="QH4" s="4">
-        <v>526612300</v>
+        <v>-5266862700</v>
       </c>
       <c r="QI4" s="4">
         <v>177242794856</v>
@@ -2755,19 +2755,19 @@
         <v>172055440671</v>
       </c>
       <c r="QL4" s="4">
-        <v>171966516956</v>
+        <v>178499796756</v>
       </c>
       <c r="QM4" s="4">
-        <v>-88923715</v>
+        <v>6444356085</v>
       </c>
       <c r="QN4" s="4">
-        <v>-101.71424028182105</v>
+        <v>24.23204306416567</v>
       </c>
       <c r="QO4" s="4">
         <v>2574678200</v>
       </c>
       <c r="QP4" s="4">
-        <v>-5276277900</v>
+        <v>1257001900</v>
       </c>
     </row>
     <row r="5">
@@ -3491,10 +3491,10 @@
         <v>14576783400</v>
       </c>
       <c r="JJ6" s="4">
-        <v>14224314600</v>
+        <v>15132836200</v>
       </c>
       <c r="JK6" s="4">
-        <v>-352468800</v>
+        <v>556052800</v>
       </c>
       <c r="JL6" s="4">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>17947673900</v>
       </c>
       <c r="JN6" s="4">
-        <v>352468800</v>
+        <v>-556052800</v>
       </c>
       <c r="JO6" s="4">
         <v>15168178900</v>
@@ -3515,19 +3515,19 @@
         <v>14887600025</v>
       </c>
       <c r="JR6" s="4">
-        <v>14537887100</v>
+        <v>15446408700</v>
       </c>
       <c r="JS6" s="4">
-        <v>-349712925</v>
+        <v>558808675</v>
       </c>
       <c r="JT6" s="4">
-        <v>224.63979157375977</v>
+        <v>-99.16277552969731</v>
       </c>
       <c r="JU6" s="4">
         <v>146062430</v>
       </c>
       <c r="JV6" s="4">
-        <v>630291800</v>
+        <v>-278229800</v>
       </c>
       <c r="JW6" s="4">
         <v>217093000</v>
@@ -3731,10 +3731,10 @@
         <v>64719690900</v>
       </c>
       <c r="QD6" s="4">
-        <v>64372124200</v>
+        <v>65280645800</v>
       </c>
       <c r="QE6" s="4">
-        <v>-347566700</v>
+        <v>560954900</v>
       </c>
       <c r="QF6" s="4">
         <v>0</v>
@@ -3743,7 +3743,7 @@
         <v>24061379608</v>
       </c>
       <c r="QH6" s="4">
-        <v>347566700</v>
+        <v>-560954900</v>
       </c>
       <c r="QI6" s="4">
         <v>66694531100</v>
@@ -3755,19 +3755,19 @@
         <v>66177754810</v>
       </c>
       <c r="QL6" s="4">
-        <v>65940384100</v>
+        <v>66848905700</v>
       </c>
       <c r="QM6" s="4">
-        <v>-237370710</v>
+        <v>671150890</v>
       </c>
       <c r="QN6" s="4">
-        <v>-145.9329722731668</v>
+        <v>29.87261664036483</v>
       </c>
       <c r="QO6" s="4">
         <v>150770630</v>
       </c>
       <c r="QP6" s="4">
-        <v>-754147000</v>
+        <v>154374600</v>
       </c>
     </row>
     <row r="7">
@@ -3859,19 +3859,19 @@
         <v>27043900</v>
       </c>
       <c r="BB7" s="4">
-        <v>39941000</v>
+        <v>37814500</v>
       </c>
       <c r="BC7" s="4">
-        <v>12897100</v>
+        <v>10770600</v>
       </c>
       <c r="BD7" s="4">
-        <v>11.433790456046863</v>
+        <v>26.036766675136143</v>
       </c>
       <c r="BE7" s="4">
         <v>19538000</v>
       </c>
       <c r="BF7" s="4">
-        <v>1665000</v>
+        <v>3791500</v>
       </c>
       <c r="BG7" s="4">
         <v>5900400</v>
@@ -3883,19 +3883,19 @@
         <v>3835260</v>
       </c>
       <c r="BJ7" s="4">
-        <v>5900400</v>
+        <v>4503700</v>
       </c>
       <c r="BK7" s="4">
-        <v>2065140</v>
+        <v>668440</v>
       </c>
       <c r="BL7" s="4">
-        <v>0</v>
+        <v>67.63221863893006</v>
       </c>
       <c r="BM7" s="4">
         <v>6012500</v>
       </c>
       <c r="BN7" s="4">
-        <v>0</v>
+        <v>1396700</v>
       </c>
       <c r="BO7" s="4">
         <v>38110300</v>
@@ -3907,19 +3907,19 @@
         <v>24771695</v>
       </c>
       <c r="BR7" s="4">
-        <v>38110300</v>
+        <v>38109700</v>
       </c>
       <c r="BS7" s="4">
-        <v>13338605</v>
+        <v>13338005</v>
       </c>
       <c r="BT7" s="4">
-        <v>0</v>
+        <v>0.004498221515668243</v>
       </c>
       <c r="BU7" s="4">
         <v>143574675</v>
       </c>
       <c r="BV7" s="4">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="CE7" s="4">
         <v>6386000</v>
@@ -4075,19 +4075,19 @@
         <v>17313652841</v>
       </c>
       <c r="FJ7" s="4">
-        <v>17369134621</v>
+        <v>17365610821</v>
       </c>
       <c r="FK7" s="4">
-        <v>55481780</v>
+        <v>51957980</v>
       </c>
       <c r="FL7" s="4">
-        <v>66.77066770607813</v>
+        <v>68.88115372756702</v>
       </c>
       <c r="FM7" s="4">
         <v>251688419</v>
       </c>
       <c r="FN7" s="4">
-        <v>111484500</v>
+        <v>115008300</v>
       </c>
       <c r="FO7" s="4">
         <v>6600000</v>
@@ -4123,19 +4123,19 @@
         <v>49176000</v>
       </c>
       <c r="FZ7" s="4">
-        <v>98352000</v>
+        <v>257072000</v>
       </c>
       <c r="GA7" s="4">
-        <v>49176000</v>
+        <v>207896000</v>
       </c>
       <c r="GB7" s="4">
-        <v>0</v>
+        <v>-322.75906946477954</v>
       </c>
       <c r="GC7" s="4">
         <v>28526200</v>
       </c>
       <c r="GD7" s="4">
-        <v>0</v>
+        <v>-158720000</v>
       </c>
       <c r="HC7" s="4">
         <v>120177600</v>
@@ -4195,19 +4195,19 @@
         <v>6038500</v>
       </c>
       <c r="HV7" s="4">
-        <v>0</v>
+        <v>3523800</v>
       </c>
       <c r="HW7" s="4">
-        <v>-6038500</v>
+        <v>-2514700</v>
       </c>
       <c r="HX7" s="4">
-        <v>285.7142857142857</v>
+        <v>177.33968937413502</v>
       </c>
       <c r="HY7" s="4">
         <v>6012500</v>
       </c>
       <c r="HZ7" s="4">
-        <v>9290000</v>
+        <v>5766200</v>
       </c>
       <c r="IA7" s="4">
         <v>335398850</v>
@@ -4243,10 +4243,10 @@
         <v>18771280885</v>
       </c>
       <c r="JJ7" s="4">
-        <v>18368455395</v>
+        <v>18557305395</v>
       </c>
       <c r="JK7" s="4">
-        <v>-402825490</v>
+        <v>-213975490</v>
       </c>
       <c r="JL7" s="4">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>8818361535</v>
       </c>
       <c r="JN7" s="4">
-        <v>402825490</v>
+        <v>213975490</v>
       </c>
       <c r="JO7" s="4">
         <v>19360950335</v>
@@ -4267,19 +4267,19 @@
         <v>19138823227.5</v>
       </c>
       <c r="JR7" s="4">
-        <v>18928983845</v>
+        <v>19280077645</v>
       </c>
       <c r="JS7" s="4">
-        <v>-209839382.5</v>
+        <v>141254417.5</v>
       </c>
       <c r="JT7" s="4">
-        <v>194.46815603088876</v>
+        <v>36.408293841398894</v>
       </c>
       <c r="JU7" s="4">
         <v>205292904</v>
       </c>
       <c r="JV7" s="4">
-        <v>431966490</v>
+        <v>80872690</v>
       </c>
       <c r="JW7" s="4">
         <v>65897000</v>
@@ -4315,19 +4315,19 @@
         <v>49176000</v>
       </c>
       <c r="KH7" s="4">
-        <v>98352000</v>
+        <v>257072000</v>
       </c>
       <c r="KI7" s="4">
-        <v>49176000</v>
+        <v>207896000</v>
       </c>
       <c r="KJ7" s="4">
-        <v>0</v>
+        <v>-322.75906946477954</v>
       </c>
       <c r="KK7" s="4">
         <v>28526200</v>
       </c>
       <c r="KL7" s="4">
-        <v>0</v>
+        <v>-158720000</v>
       </c>
       <c r="LC7" s="4">
         <v>89835000</v>
@@ -4387,19 +4387,19 @@
         <v>39947050</v>
       </c>
       <c r="LV7" s="4">
-        <v>39941000</v>
+        <v>37814500</v>
       </c>
       <c r="LW7" s="4">
-        <v>-6050</v>
+        <v>-2132550</v>
       </c>
       <c r="LX7" s="4">
-        <v>100.02812651819275</v>
+        <v>109.91424898709667</v>
       </c>
       <c r="LY7" s="4">
         <v>19538000</v>
       </c>
       <c r="LZ7" s="4">
-        <v>21516000</v>
+        <v>23642500</v>
       </c>
       <c r="MA7" s="4">
         <v>15190400</v>
@@ -4411,19 +4411,19 @@
         <v>9873760</v>
       </c>
       <c r="MD7" s="4">
-        <v>5900400</v>
+        <v>8027500</v>
       </c>
       <c r="ME7" s="4">
-        <v>-3973360</v>
+        <v>-1846260</v>
       </c>
       <c r="MF7" s="4">
-        <v>174.73441873062689</v>
+        <v>134.7260675915616</v>
       </c>
       <c r="MG7" s="4">
         <v>6012500</v>
       </c>
       <c r="MH7" s="4">
-        <v>9290000</v>
+        <v>7162900</v>
       </c>
       <c r="MQ7" s="4">
         <v>335398850</v>
@@ -4483,10 +4483,10 @@
         <v>34996949106</v>
       </c>
       <c r="QD7" s="4">
-        <v>34569940416</v>
+        <v>34758790416</v>
       </c>
       <c r="QE7" s="4">
-        <v>-427008690</v>
+        <v>-238158690</v>
       </c>
       <c r="QF7" s="4">
         <v>0</v>
@@ -4495,7 +4495,7 @@
         <v>11939587949</v>
       </c>
       <c r="QH7" s="4">
-        <v>427008690</v>
+        <v>238158690</v>
       </c>
       <c r="QI7" s="4">
         <v>36841569456</v>
@@ -4507,19 +4507,19 @@
         <v>36452476068.5</v>
       </c>
       <c r="QL7" s="4">
-        <v>36298118466</v>
+        <v>36645688466</v>
       </c>
       <c r="QM7" s="4">
-        <v>-154357602.5</v>
+        <v>193212397.5</v>
       </c>
       <c r="QN7" s="4">
-        <v>-139.6710937422446</v>
+        <v>-50.342924421967986</v>
       </c>
       <c r="QO7" s="4">
         <v>378258579</v>
       </c>
       <c r="QP7" s="4">
-        <v>-543450990</v>
+        <v>-195880990</v>
       </c>
     </row>
     <row r="8">
@@ -4923,10 +4923,10 @@
         <v>43681497500</v>
       </c>
       <c r="JJ8" s="4">
-        <v>4901428900</v>
+        <v>9139738883</v>
       </c>
       <c r="JK8" s="4">
-        <v>-38780068600</v>
+        <v>-34541758617</v>
       </c>
       <c r="JL8" s="4">
         <v>0</v>
@@ -4935,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="JN8" s="4">
-        <v>38780068600</v>
+        <v>34541758617</v>
       </c>
       <c r="JO8" s="4">
         <v>44517967900</v>
@@ -4947,19 +4947,19 @@
         <v>44105843160</v>
       </c>
       <c r="JR8" s="4">
-        <v>5297379900</v>
+        <v>9535689883</v>
       </c>
       <c r="JS8" s="4">
-        <v>-38808463260</v>
+        <v>-34570153277</v>
       </c>
       <c r="JT8" s="4">
-        <v>9516.678857959365</v>
+        <v>8488.274209648273</v>
       </c>
       <c r="JU8" s="4">
         <v>64350000</v>
       </c>
       <c r="JV8" s="4">
-        <v>39220588000</v>
+        <v>34982278017</v>
       </c>
       <c r="JW8" s="4">
         <v>758248000</v>
@@ -5091,10 +5091,10 @@
         <v>52943632265</v>
       </c>
       <c r="QD8" s="4">
-        <v>14127698065</v>
+        <v>18366008048</v>
       </c>
       <c r="QE8" s="4">
-        <v>-38815934200</v>
+        <v>-34577624217</v>
       </c>
       <c r="QF8" s="4">
         <v>0</v>
@@ -5103,7 +5103,7 @@
         <v>3656875399</v>
       </c>
       <c r="QH8" s="4">
-        <v>38815934200</v>
+        <v>34577624217</v>
       </c>
       <c r="QI8" s="4">
         <v>54248174765</v>
@@ -5115,19 +5115,19 @@
         <v>53636620190</v>
       </c>
       <c r="QL8" s="4">
-        <v>14835471565</v>
+        <v>19073781548</v>
       </c>
       <c r="QM8" s="4">
-        <v>-38801148625</v>
+        <v>-34562838642</v>
       </c>
       <c r="QN8" s="4">
-        <v>-6444.674737328226</v>
+        <v>-5751.636019892419</v>
       </c>
       <c r="QO8" s="4">
         <v>64350000</v>
       </c>
       <c r="QP8" s="4">
-        <v>-39412703200</v>
+        <v>-35174393217</v>
       </c>
     </row>
     <row r="9">
@@ -7235,19 +7235,19 @@
         <v>46275000</v>
       </c>
       <c r="GH12" s="4">
-        <v>63150000</v>
+        <v>102650000</v>
       </c>
       <c r="GI12" s="4">
-        <v>16875000</v>
+        <v>56375000</v>
       </c>
       <c r="GJ12" s="4">
-        <v>63.533225283630465</v>
+        <v>-21.82603997839006</v>
       </c>
       <c r="GK12" s="4">
         <v>54050000</v>
       </c>
       <c r="GL12" s="4">
-        <v>29400000</v>
+        <v>-10100000</v>
       </c>
       <c r="GM12" s="4">
         <v>9750000</v>
@@ -7355,10 +7355,10 @@
         <v>323277800</v>
       </c>
       <c r="JJ12" s="4">
-        <v>276574800</v>
+        <v>737074600</v>
       </c>
       <c r="JK12" s="4">
-        <v>-46703000</v>
+        <v>413796800</v>
       </c>
       <c r="JL12" s="4">
         <v>0</v>
@@ -7367,7 +7367,7 @@
         <v>10119600</v>
       </c>
       <c r="JN12" s="4">
-        <v>46703000</v>
+        <v>-413796800</v>
       </c>
       <c r="JO12" s="4">
         <v>499999500</v>
@@ -7379,19 +7379,19 @@
         <v>414797305</v>
       </c>
       <c r="JR12" s="4">
-        <v>392505100</v>
+        <v>892504900</v>
       </c>
       <c r="JS12" s="4">
-        <v>-22292205</v>
+        <v>477707595</v>
       </c>
       <c r="JT12" s="4">
-        <v>126.16388580129889</v>
+        <v>-460.67522086725586</v>
       </c>
       <c r="JU12" s="4">
         <v>151595245</v>
       </c>
       <c r="JV12" s="4">
-        <v>107494400</v>
+        <v>-392505400</v>
       </c>
       <c r="JW12" s="4">
         <v>132964000</v>
@@ -7427,19 +7427,19 @@
         <v>51275000</v>
       </c>
       <c r="KP12" s="4">
-        <v>63150000</v>
+        <v>102650000</v>
       </c>
       <c r="KQ12" s="4">
-        <v>11875000</v>
+        <v>51375000</v>
       </c>
       <c r="KR12" s="4">
-        <v>76.84056557776694</v>
+        <v>-0.19502681618722573</v>
       </c>
       <c r="KS12" s="4">
         <v>54050000</v>
       </c>
       <c r="KT12" s="4">
-        <v>39400000</v>
+        <v>-100000</v>
       </c>
       <c r="KU12" s="4">
         <v>9750000</v>
@@ -7547,10 +7547,10 @@
         <v>3516843161</v>
       </c>
       <c r="QD12" s="4">
-        <v>3476643161</v>
+        <v>3936643161</v>
       </c>
       <c r="QE12" s="4">
-        <v>-40200000</v>
+        <v>419800000</v>
       </c>
       <c r="QF12" s="4">
         <v>0</v>
@@ -7559,7 +7559,7 @@
         <v>1193560853</v>
       </c>
       <c r="QH12" s="4">
-        <v>40200000</v>
+        <v>-419800000</v>
       </c>
       <c r="QI12" s="4">
         <v>3903388461</v>
@@ -7571,19 +7571,19 @@
         <v>3735008486</v>
       </c>
       <c r="QL12" s="4">
-        <v>3758617261</v>
+        <v>4258617061</v>
       </c>
       <c r="QM12" s="4">
-        <v>23608775</v>
+        <v>523608575</v>
       </c>
       <c r="QN12" s="4">
-        <v>-85.97887011207835</v>
+        <v>210.96843612193194</v>
       </c>
       <c r="QO12" s="4">
         <v>180022845</v>
       </c>
       <c r="QP12" s="4">
-        <v>-144771200</v>
+        <v>355228600</v>
       </c>
     </row>
     <row r="13">
@@ -7651,19 +7651,19 @@
         <v>54923500</v>
       </c>
       <c r="AL13" s="4">
-        <v>59670000</v>
+        <v>32468000</v>
       </c>
       <c r="AM13" s="4">
-        <v>4746500</v>
+        <v>-22455500</v>
       </c>
       <c r="AN13" s="4">
-        <v>91.35797973545021</v>
+        <v>140.88504920480304</v>
       </c>
       <c r="AO13" s="4">
         <v>14684080</v>
       </c>
       <c r="AP13" s="4">
-        <v>50177000</v>
+        <v>77379000</v>
       </c>
       <c r="AQ13" s="4">
         <v>8750400</v>
@@ -7819,19 +7819,19 @@
         <v>3445788006</v>
       </c>
       <c r="FJ13" s="4">
-        <v>3529861576</v>
+        <v>3502659576</v>
       </c>
       <c r="FK13" s="4">
-        <v>84073570</v>
+        <v>56871570</v>
       </c>
       <c r="FL13" s="4">
-        <v>38.80652831721022</v>
+        <v>58.60567347918262</v>
       </c>
       <c r="FM13" s="4">
         <v>96053780</v>
       </c>
       <c r="FN13" s="4">
-        <v>53316200</v>
+        <v>80518200</v>
       </c>
       <c r="JW13" s="4">
         <v>63146000</v>
@@ -7891,19 +7891,19 @@
         <v>54923500</v>
       </c>
       <c r="LF13" s="4">
-        <v>59670000</v>
+        <v>32468000</v>
       </c>
       <c r="LG13" s="4">
-        <v>4746500</v>
+        <v>-22455500</v>
       </c>
       <c r="LH13" s="4">
-        <v>91.35797973545021</v>
+        <v>140.88504920480304</v>
       </c>
       <c r="LI13" s="4">
         <v>14684080</v>
       </c>
       <c r="LJ13" s="4">
-        <v>50177000</v>
+        <v>77379000</v>
       </c>
       <c r="LK13" s="4">
         <v>8750400</v>
@@ -8011,19 +8011,19 @@
         <v>3445788006</v>
       </c>
       <c r="QL13" s="4">
-        <v>3529861576</v>
+        <v>3502659576</v>
       </c>
       <c r="QM13" s="4">
-        <v>84073570</v>
+        <v>56871570</v>
       </c>
       <c r="QN13" s="4">
-        <v>-38.80652831721022</v>
+        <v>-58.60567347918262</v>
       </c>
       <c r="QO13" s="4">
         <v>96053780</v>
       </c>
       <c r="QP13" s="4">
-        <v>-53316200</v>
+        <v>-80518200</v>
       </c>
     </row>
     <row r="14">
@@ -9403,10 +9403,10 @@
         <v>2000000000</v>
       </c>
       <c r="JJ16" s="4">
-        <v>2000000000</v>
+        <v>2475000000</v>
       </c>
       <c r="JK16" s="4">
-        <v>0</v>
+        <v>475000000</v>
       </c>
       <c r="JL16" s="4">
         <v>0</v>
@@ -9415,7 +9415,7 @@
         <v>598800000</v>
       </c>
       <c r="JN16" s="4">
-        <v>0</v>
+        <v>-475000000</v>
       </c>
       <c r="JO16" s="4">
         <v>2000000000</v>
@@ -9427,19 +9427,19 @@
         <v>2000000000</v>
       </c>
       <c r="JR16" s="4">
-        <v>2000000000</v>
+        <v>2475000000</v>
       </c>
       <c r="JS16" s="4">
-        <v>0</v>
+        <v>475000000</v>
       </c>
       <c r="JT16" s="4">
-        <v>NaN</v>
+        <v>Infinity</v>
       </c>
       <c r="JU16" s="4">
         <v>0</v>
       </c>
       <c r="JV16" s="4">
-        <v>0</v>
+        <v>-475000000</v>
       </c>
       <c r="JW16" s="4">
         <v>327407000</v>
@@ -9619,19 +9619,19 @@
         <v>4983851379</v>
       </c>
       <c r="QL16" s="4">
-        <v>4986883729</v>
+        <v>5461883729</v>
       </c>
       <c r="QM16" s="4">
-        <v>3032350</v>
+        <v>478032350</v>
       </c>
       <c r="QN16" s="4">
-        <v>-98.89212003546122</v>
+        <v>74.65083613909668</v>
       </c>
       <c r="QO16" s="4">
         <v>732626400</v>
       </c>
       <c r="QP16" s="4">
-        <v>-270675100</v>
+        <v>204324900</v>
       </c>
     </row>
     <row r="17">
@@ -10235,19 +10235,19 @@
         <v>18185050</v>
       </c>
       <c r="BB18" s="4">
-        <v>21789900</v>
+        <v>25211300</v>
       </c>
       <c r="BC18" s="4">
-        <v>3604850</v>
+        <v>7026250</v>
       </c>
       <c r="BD18" s="4">
-        <v>63.18557590673972</v>
+        <v>28.244629517103338</v>
       </c>
       <c r="BE18" s="4">
         <v>21387000</v>
       </c>
       <c r="BF18" s="4">
-        <v>6187100</v>
+        <v>2765700</v>
       </c>
       <c r="BG18" s="4">
         <v>5279400</v>
@@ -10283,19 +10283,19 @@
         <v>18819320</v>
       </c>
       <c r="BR18" s="4">
-        <v>23972800</v>
+        <v>25172800</v>
       </c>
       <c r="BS18" s="4">
-        <v>5153480</v>
+        <v>6353480</v>
       </c>
       <c r="BT18" s="4">
-        <v>49.14402554699866</v>
+        <v>37.302091680252</v>
       </c>
       <c r="BU18" s="4">
         <v>11772400</v>
       </c>
       <c r="BV18" s="4">
-        <v>4980000</v>
+        <v>3780000</v>
       </c>
       <c r="CE18" s="4">
         <v>26500000</v>
@@ -10331,10 +10331,10 @@
         <v>3942678207</v>
       </c>
       <c r="FB18" s="4">
-        <v>3942728307</v>
+        <v>4044149035</v>
       </c>
       <c r="FC18" s="4">
-        <v>50100</v>
+        <v>101470828</v>
       </c>
       <c r="FD18" s="4">
         <v>0</v>
@@ -10343,7 +10343,7 @@
         <v>1551537600</v>
       </c>
       <c r="FF18" s="4">
-        <v>-50100</v>
+        <v>-101470828</v>
       </c>
       <c r="FG18" s="4">
         <v>4163067407</v>
@@ -10355,19 +10355,19 @@
         <v>4066179187</v>
       </c>
       <c r="FJ18" s="4">
-        <v>4113038607</v>
+        <v>4219080735</v>
       </c>
       <c r="FK18" s="4">
-        <v>46859420</v>
+        <v>152901548</v>
       </c>
       <c r="FL18" s="4">
-        <v>51.6355858328288</v>
+        <v>-57.812320218082235</v>
       </c>
       <c r="FM18" s="4">
         <v>110978460</v>
       </c>
       <c r="FN18" s="4">
-        <v>50028800</v>
+        <v>-56013328</v>
       </c>
       <c r="GE18" s="4">
         <v>259700000</v>
@@ -10403,19 +10403,19 @@
         <v>206929500</v>
       </c>
       <c r="GX18" s="4">
-        <v>290489000</v>
+        <v>359312000</v>
       </c>
       <c r="GY18" s="4">
-        <v>83559500</v>
+        <v>152382500</v>
       </c>
       <c r="GZ18" s="4">
-        <v>59.619338953604974</v>
+        <v>26.360185473796633</v>
       </c>
       <c r="HA18" s="4">
         <v>65556260</v>
       </c>
       <c r="HB18" s="4">
-        <v>123370000</v>
+        <v>54547000</v>
       </c>
       <c r="HK18" s="4">
         <v>14896000</v>
@@ -10499,10 +10499,10 @@
         <v>50661600</v>
       </c>
       <c r="JJ18" s="4">
-        <v>25327400</v>
+        <v>24903800</v>
       </c>
       <c r="JK18" s="4">
-        <v>-25334200</v>
+        <v>-25757800</v>
       </c>
       <c r="JL18" s="4">
         <v>0</v>
@@ -10511,7 +10511,7 @@
         <v>13241200</v>
       </c>
       <c r="JN18" s="4">
-        <v>25334200</v>
+        <v>25757800</v>
       </c>
       <c r="JO18" s="4">
         <v>899615300</v>
@@ -10523,19 +10523,19 @@
         <v>501447655</v>
       </c>
       <c r="JR18" s="4">
-        <v>454132100</v>
+        <v>522531500</v>
       </c>
       <c r="JS18" s="4">
-        <v>-47315555</v>
+        <v>21083845</v>
       </c>
       <c r="JT18" s="4">
-        <v>111.88332492460556</v>
+        <v>94.70478195183338</v>
       </c>
       <c r="JU18" s="4">
         <v>99206060</v>
       </c>
       <c r="JV18" s="4">
-        <v>445483200</v>
+        <v>377083800</v>
       </c>
       <c r="KM18" s="4">
         <v>305400000</v>
@@ -10571,19 +10571,19 @@
         <v>249919500</v>
       </c>
       <c r="LF18" s="4">
-        <v>353105000</v>
+        <v>421928000</v>
       </c>
       <c r="LG18" s="4">
-        <v>103185500</v>
+        <v>172008500</v>
       </c>
       <c r="LH18" s="4">
-        <v>58.712505426747406</v>
+        <v>31.174438169090447</v>
       </c>
       <c r="LI18" s="4">
         <v>65556260</v>
       </c>
       <c r="LJ18" s="4">
-        <v>146734000</v>
+        <v>77911000</v>
       </c>
       <c r="LS18" s="4">
         <v>42873000</v>
@@ -10595,19 +10595,19 @@
         <v>27867450</v>
       </c>
       <c r="LV18" s="4">
-        <v>30756900</v>
+        <v>34178300</v>
       </c>
       <c r="LW18" s="4">
-        <v>2889450</v>
+        <v>6310850</v>
       </c>
       <c r="LX18" s="4">
-        <v>80.74412467387067</v>
+        <v>57.94322767242788</v>
       </c>
       <c r="LY18" s="4">
         <v>21387000</v>
       </c>
       <c r="LZ18" s="4">
-        <v>12116100</v>
+        <v>8694700</v>
       </c>
       <c r="MA18" s="4">
         <v>7778100</v>
@@ -10667,10 +10667,10 @@
         <v>3960468207</v>
       </c>
       <c r="QD18" s="4">
-        <v>3954099307</v>
+        <v>4055520035</v>
       </c>
       <c r="QE18" s="4">
-        <v>-6368900</v>
+        <v>95051828</v>
       </c>
       <c r="QF18" s="4">
         <v>0</v>
@@ -10679,7 +10679,7 @@
         <v>1551537600</v>
       </c>
       <c r="QH18" s="4">
-        <v>6368900</v>
+        <v>-95051828</v>
       </c>
       <c r="QI18" s="4">
         <v>5062682707</v>
@@ -10691,19 +10691,19 @@
         <v>4567626842</v>
       </c>
       <c r="QL18" s="4">
-        <v>4567170707</v>
+        <v>4741612235</v>
       </c>
       <c r="QM18" s="4">
-        <v>-456135</v>
+        <v>173985393</v>
       </c>
       <c r="QN18" s="4">
-        <v>-100.09213808627437</v>
+        <v>-64.85540212719225</v>
       </c>
       <c r="QO18" s="4">
         <v>110978460</v>
       </c>
       <c r="QP18" s="4">
-        <v>-495512000</v>
+        <v>-321070472</v>
       </c>
     </row>
     <row r="19">
@@ -10723,19 +10723,19 @@
         <v>42393600</v>
       </c>
       <c r="F19" s="4">
-        <v>48854840</v>
+        <v>48794640</v>
       </c>
       <c r="G19" s="4">
-        <v>6461240</v>
+        <v>6401040</v>
       </c>
       <c r="H19" s="4">
-        <v>84.75892587560386</v>
+        <v>84.90092844202898</v>
       </c>
       <c r="I19" s="4">
         <v>21969743</v>
       </c>
       <c r="J19" s="4">
-        <v>35932360</v>
+        <v>35992560</v>
       </c>
       <c r="S19" s="4">
         <v>68400000</v>
@@ -10939,19 +10939,19 @@
         <v>1881255930</v>
       </c>
       <c r="FJ19" s="4">
-        <v>1881444010</v>
+        <v>1881383810</v>
       </c>
       <c r="FK19" s="4">
-        <v>188080</v>
+        <v>127880</v>
       </c>
       <c r="FL19" s="4">
-        <v>99.8419839981073</v>
+        <v>99.89256121691812</v>
       </c>
       <c r="FM19" s="4">
         <v>239110335</v>
       </c>
       <c r="FN19" s="4">
-        <v>118837840</v>
+        <v>118898040</v>
       </c>
       <c r="JW19" s="4">
         <v>84787200</v>
@@ -10963,19 +10963,19 @@
         <v>42393600</v>
       </c>
       <c r="JZ19" s="4">
-        <v>48854840</v>
+        <v>48794640</v>
       </c>
       <c r="KA19" s="4">
-        <v>6461240</v>
+        <v>6401040</v>
       </c>
       <c r="KB19" s="4">
-        <v>84.75892587560386</v>
+        <v>84.90092844202898</v>
       </c>
       <c r="KC19" s="4">
         <v>21969743</v>
       </c>
       <c r="KD19" s="4">
-        <v>35932360</v>
+        <v>35992560</v>
       </c>
       <c r="KM19" s="4">
         <v>68400000</v>
@@ -11107,19 +11107,19 @@
         <v>1881255930</v>
       </c>
       <c r="QL19" s="4">
-        <v>1881444010</v>
+        <v>1881383810</v>
       </c>
       <c r="QM19" s="4">
-        <v>188080</v>
+        <v>127880</v>
       </c>
       <c r="QN19" s="4">
-        <v>-99.8419839981073</v>
+        <v>-99.89256121691812</v>
       </c>
       <c r="QO19" s="4">
         <v>239110335</v>
       </c>
       <c r="QP19" s="4">
-        <v>-118837840</v>
+        <v>-118898040</v>
       </c>
     </row>
     <row r="20">
@@ -11139,19 +11139,19 @@
         <v>127636000</v>
       </c>
       <c r="F20" s="4">
-        <v>123459000</v>
+        <v>255272000</v>
       </c>
       <c r="G20" s="4">
-        <v>-4177000</v>
+        <v>127636000</v>
       </c>
       <c r="H20" s="4">
-        <v>103.27258767118994</v>
+        <v>0</v>
       </c>
       <c r="I20" s="4">
         <v>38255600</v>
       </c>
       <c r="J20" s="4">
-        <v>131813000</v>
+        <v>0</v>
       </c>
       <c r="S20" s="4">
         <v>112800000</v>
@@ -11379,19 +11379,19 @@
         <v>3736379628</v>
       </c>
       <c r="FJ20" s="4">
-        <v>3736371603</v>
+        <v>3868184603</v>
       </c>
       <c r="FK20" s="4">
-        <v>-8025</v>
+        <v>131804975</v>
       </c>
       <c r="FL20" s="4">
-        <v>100.00326577984634</v>
+        <v>46.36186529543252</v>
       </c>
       <c r="FM20" s="4">
         <v>92263800</v>
       </c>
       <c r="FN20" s="4">
-        <v>245738000</v>
+        <v>113925000</v>
       </c>
       <c r="JW20" s="4">
         <v>255272000</v>
@@ -11403,19 +11403,19 @@
         <v>127636000</v>
       </c>
       <c r="JZ20" s="4">
-        <v>123459000</v>
+        <v>255272000</v>
       </c>
       <c r="KA20" s="4">
-        <v>-4177000</v>
+        <v>127636000</v>
       </c>
       <c r="KB20" s="4">
-        <v>103.27258767118994</v>
+        <v>0</v>
       </c>
       <c r="KC20" s="4">
         <v>38255600</v>
       </c>
       <c r="KD20" s="4">
-        <v>131813000</v>
+        <v>0</v>
       </c>
       <c r="KM20" s="4">
         <v>112800000</v>
@@ -11547,19 +11547,19 @@
         <v>3736379628</v>
       </c>
       <c r="QL20" s="4">
-        <v>3736371603</v>
+        <v>3868184603</v>
       </c>
       <c r="QM20" s="4">
-        <v>-8025</v>
+        <v>131804975</v>
       </c>
       <c r="QN20" s="4">
-        <v>-100.00326577984634</v>
+        <v>-46.36186529543252</v>
       </c>
       <c r="QO20" s="4">
         <v>92263800</v>
       </c>
       <c r="QP20" s="4">
-        <v>-245738000</v>
+        <v>-113925000</v>
       </c>
     </row>
     <row r="21">
@@ -12139,19 +12139,19 @@
         <v>82688500</v>
       </c>
       <c r="F22" s="4">
-        <v>81375000</v>
+        <v>100965000</v>
       </c>
       <c r="G22" s="4">
-        <v>-1313500</v>
+        <v>18276500</v>
       </c>
       <c r="H22" s="4">
-        <v>101.58849174915497</v>
+        <v>77.8971682882142</v>
       </c>
       <c r="I22" s="4">
         <v>20176620</v>
       </c>
       <c r="J22" s="4">
-        <v>84002000</v>
+        <v>64412000</v>
       </c>
       <c r="S22" s="4">
         <v>57100000</v>
@@ -12163,19 +12163,19 @@
         <v>28550000</v>
       </c>
       <c r="V22" s="4">
-        <v>30500000</v>
+        <v>106000000</v>
       </c>
       <c r="W22" s="4">
-        <v>1950000</v>
+        <v>77450000</v>
       </c>
       <c r="X22" s="4">
-        <v>93.16987740805604</v>
+        <v>-171.2784588441331</v>
       </c>
       <c r="Y22" s="4">
         <v>14550000</v>
       </c>
       <c r="Z22" s="4">
-        <v>26600000</v>
+        <v>-48900000</v>
       </c>
       <c r="AY22" s="4">
         <v>28605400</v>
@@ -12187,19 +12187,19 @@
         <v>18593510</v>
       </c>
       <c r="BB22" s="4">
-        <v>18970400</v>
+        <v>20983200</v>
       </c>
       <c r="BC22" s="4">
-        <v>376890</v>
+        <v>2389690</v>
       </c>
       <c r="BD22" s="4">
-        <v>96.2355759002546</v>
+        <v>76.13147967067158</v>
       </c>
       <c r="BE22" s="4">
         <v>4835600</v>
       </c>
       <c r="BF22" s="4">
-        <v>9635000</v>
+        <v>7622200</v>
       </c>
       <c r="BG22" s="4">
         <v>21872600</v>
@@ -12211,19 +12211,19 @@
         <v>14217190</v>
       </c>
       <c r="BJ22" s="4">
-        <v>14178300</v>
+        <v>15850500</v>
       </c>
       <c r="BK22" s="4">
-        <v>-38890</v>
+        <v>1633310</v>
       </c>
       <c r="BL22" s="4">
-        <v>100.50800675600655</v>
+        <v>78.66463063376096</v>
       </c>
       <c r="BM22" s="4">
         <v>3939900</v>
       </c>
       <c r="BN22" s="4">
-        <v>7694300</v>
+        <v>6022100</v>
       </c>
       <c r="BO22" s="4">
         <v>7535500</v>
@@ -12235,19 +12235,19 @@
         <v>4898075</v>
       </c>
       <c r="BR22" s="4">
-        <v>4368900</v>
+        <v>5426900</v>
       </c>
       <c r="BS22" s="4">
-        <v>-529175</v>
+        <v>528825</v>
       </c>
       <c r="BT22" s="4">
-        <v>120.0640776514972</v>
+        <v>79.94919286804364</v>
       </c>
       <c r="BU22" s="4">
         <v>0</v>
       </c>
       <c r="BV22" s="4">
-        <v>3166600</v>
+        <v>2108600</v>
       </c>
       <c r="CE22" s="4">
         <v>8265000</v>
@@ -12403,10 +12403,10 @@
         <v>2569004622</v>
       </c>
       <c r="FB22" s="4">
-        <v>2569004622</v>
+        <v>2569171622</v>
       </c>
       <c r="FC22" s="4">
-        <v>0</v>
+        <v>167000</v>
       </c>
       <c r="FD22" s="4">
         <v>0</v>
@@ -12415,7 +12415,7 @@
         <v>1036452249</v>
       </c>
       <c r="FF22" s="4">
-        <v>0</v>
+        <v>-167000</v>
       </c>
       <c r="FG22" s="4">
         <v>2868160122</v>
@@ -12427,19 +12427,19 @@
         <v>2730084147</v>
       </c>
       <c r="FJ22" s="4">
-        <v>2730070222</v>
+        <v>2830070222</v>
       </c>
       <c r="FK22" s="4">
-        <v>-13925</v>
+        <v>99986075</v>
       </c>
       <c r="FL22" s="4">
-        <v>100.01008502746404</v>
+        <v>27.586189414921748</v>
       </c>
       <c r="FM22" s="4">
         <v>44742120</v>
       </c>
       <c r="FN22" s="4">
-        <v>138089900</v>
+        <v>38089900</v>
       </c>
       <c r="JW22" s="4">
         <v>165377000</v>
@@ -12451,19 +12451,19 @@
         <v>82688500</v>
       </c>
       <c r="JZ22" s="4">
-        <v>81375000</v>
+        <v>100965000</v>
       </c>
       <c r="KA22" s="4">
-        <v>-1313500</v>
+        <v>18276500</v>
       </c>
       <c r="KB22" s="4">
-        <v>101.58849174915497</v>
+        <v>77.8971682882142</v>
       </c>
       <c r="KC22" s="4">
         <v>20176620</v>
       </c>
       <c r="KD22" s="4">
-        <v>84002000</v>
+        <v>64412000</v>
       </c>
       <c r="KM22" s="4">
         <v>57100000</v>
@@ -12475,19 +12475,19 @@
         <v>28550000</v>
       </c>
       <c r="KP22" s="4">
-        <v>30500000</v>
+        <v>106000000</v>
       </c>
       <c r="KQ22" s="4">
-        <v>1950000</v>
+        <v>77450000</v>
       </c>
       <c r="KR22" s="4">
-        <v>93.16987740805604</v>
+        <v>-171.2784588441331</v>
       </c>
       <c r="KS22" s="4">
         <v>14550000</v>
       </c>
       <c r="KT22" s="4">
-        <v>26600000</v>
+        <v>-48900000</v>
       </c>
       <c r="LS22" s="4">
         <v>28605400</v>
@@ -12499,19 +12499,19 @@
         <v>18593510</v>
       </c>
       <c r="LV22" s="4">
-        <v>18970400</v>
+        <v>20983200</v>
       </c>
       <c r="LW22" s="4">
-        <v>376890</v>
+        <v>2389690</v>
       </c>
       <c r="LX22" s="4">
-        <v>96.2355759002546</v>
+        <v>76.13147967067158</v>
       </c>
       <c r="LY22" s="4">
         <v>4835600</v>
       </c>
       <c r="LZ22" s="4">
-        <v>9635000</v>
+        <v>7622200</v>
       </c>
       <c r="MA22" s="4">
         <v>21872600</v>
@@ -12523,19 +12523,19 @@
         <v>14217190</v>
       </c>
       <c r="MD22" s="4">
-        <v>14178300</v>
+        <v>15850500</v>
       </c>
       <c r="ME22" s="4">
-        <v>-38890</v>
+        <v>1633310</v>
       </c>
       <c r="MF22" s="4">
-        <v>100.50800675600655</v>
+        <v>78.66463063376096</v>
       </c>
       <c r="MG22" s="4">
         <v>3939900</v>
       </c>
       <c r="MH22" s="4">
-        <v>7694300</v>
+        <v>6022100</v>
       </c>
       <c r="MY22" s="4">
         <v>8265000</v>
@@ -12595,10 +12595,10 @@
         <v>2569004622</v>
       </c>
       <c r="QD22" s="4">
-        <v>2569004622</v>
+        <v>2569171622</v>
       </c>
       <c r="QE22" s="4">
-        <v>0</v>
+        <v>167000</v>
       </c>
       <c r="QF22" s="4">
         <v>0</v>
@@ -12607,7 +12607,7 @@
         <v>1036452249</v>
       </c>
       <c r="QH22" s="4">
-        <v>0</v>
+        <v>-167000</v>
       </c>
       <c r="QI22" s="4">
         <v>2868160122</v>
@@ -12619,19 +12619,19 @@
         <v>2730084147</v>
       </c>
       <c r="QL22" s="4">
-        <v>2730070222</v>
+        <v>2830070222</v>
       </c>
       <c r="QM22" s="4">
-        <v>-13925</v>
+        <v>99986075</v>
       </c>
       <c r="QN22" s="4">
-        <v>-100.01008502746404</v>
+        <v>-27.586189414921748</v>
       </c>
       <c r="QO22" s="4">
         <v>44742120</v>
       </c>
       <c r="QP22" s="4">
-        <v>-138089900</v>
+        <v>-38089900</v>
       </c>
     </row>
     <row r="23">
@@ -12651,19 +12651,19 @@
         <v>74189500</v>
       </c>
       <c r="F23" s="4">
-        <v>71356000</v>
+        <v>113514000</v>
       </c>
       <c r="G23" s="4">
-        <v>-2833500</v>
+        <v>39324500</v>
       </c>
       <c r="H23" s="4">
-        <v>103.81927361688648</v>
+        <v>46.994520787982125</v>
       </c>
       <c r="I23" s="4">
         <v>0</v>
       </c>
       <c r="J23" s="4">
-        <v>77023000</v>
+        <v>34865000</v>
       </c>
       <c r="S23" s="4">
         <v>18600000</v>
@@ -12795,19 +12795,19 @@
         <v>10914735</v>
       </c>
       <c r="BR23" s="4">
-        <v>12291200</v>
+        <v>19761200</v>
       </c>
       <c r="BS23" s="4">
-        <v>1376465</v>
+        <v>8846465</v>
       </c>
       <c r="BT23" s="4">
-        <v>76.57943923643458</v>
+        <v>-50.52265845862759</v>
       </c>
       <c r="BU23" s="4">
         <v>3909600</v>
       </c>
       <c r="BV23" s="4">
-        <v>4500700</v>
+        <v>-2969300</v>
       </c>
       <c r="CE23" s="4">
         <v>11594000</v>
@@ -12867,10 +12867,10 @@
         <v>1974874689</v>
       </c>
       <c r="FB23" s="4">
-        <v>1970549889</v>
+        <v>1989184389</v>
       </c>
       <c r="FC23" s="4">
-        <v>-4324800</v>
+        <v>14309700</v>
       </c>
       <c r="FD23" s="4">
         <v>0</v>
@@ -12879,7 +12879,7 @@
         <v>769789031</v>
       </c>
       <c r="FF23" s="4">
-        <v>4324800</v>
+        <v>-14309700</v>
       </c>
       <c r="FG23" s="4">
         <v>2260664589</v>
@@ -12891,19 +12891,19 @@
         <v>2135591274</v>
       </c>
       <c r="FJ23" s="4">
-        <v>2135586889</v>
+        <v>2203849389</v>
       </c>
       <c r="FK23" s="4">
-        <v>-4385</v>
+        <v>68258115</v>
       </c>
       <c r="FL23" s="4">
-        <v>100.00350594369391</v>
+        <v>45.425517025754054</v>
       </c>
       <c r="FM23" s="4">
         <v>27056200</v>
       </c>
       <c r="FN23" s="4">
-        <v>125077700</v>
+        <v>56815200</v>
       </c>
       <c r="JW23" s="4">
         <v>148379000</v>
@@ -12915,19 +12915,19 @@
         <v>74189500</v>
       </c>
       <c r="JZ23" s="4">
-        <v>71356000</v>
+        <v>113514000</v>
       </c>
       <c r="KA23" s="4">
-        <v>-2833500</v>
+        <v>39324500</v>
       </c>
       <c r="KB23" s="4">
-        <v>103.81927361688648</v>
+        <v>46.994520787982125</v>
       </c>
       <c r="KC23" s="4">
         <v>0</v>
       </c>
       <c r="KD23" s="4">
-        <v>77023000</v>
+        <v>34865000</v>
       </c>
       <c r="KM23" s="4">
         <v>18600000</v>
@@ -13083,10 +13083,10 @@
         <v>1974874689</v>
       </c>
       <c r="QD23" s="4">
-        <v>1970549889</v>
+        <v>1989184389</v>
       </c>
       <c r="QE23" s="4">
-        <v>-4324800</v>
+        <v>14309700</v>
       </c>
       <c r="QF23" s="4">
         <v>0</v>
@@ -13095,7 +13095,7 @@
         <v>769789031</v>
       </c>
       <c r="QH23" s="4">
-        <v>4324800</v>
+        <v>-14309700</v>
       </c>
       <c r="QI23" s="4">
         <v>2260664589</v>
@@ -13107,19 +13107,19 @@
         <v>2135591274</v>
       </c>
       <c r="QL23" s="4">
-        <v>2135586889</v>
+        <v>2203849389</v>
       </c>
       <c r="QM23" s="4">
-        <v>-4385</v>
+        <v>68258115</v>
       </c>
       <c r="QN23" s="4">
-        <v>-100.00350594369391</v>
+        <v>-45.425517025754054</v>
       </c>
       <c r="QO23" s="4">
         <v>27056200</v>
       </c>
       <c r="QP23" s="4">
-        <v>-125077700</v>
+        <v>-56815200</v>
       </c>
     </row>
     <row r="24">
@@ -13235,19 +13235,19 @@
         <v>13680875</v>
       </c>
       <c r="BJ24" s="4">
-        <v>13652600</v>
+        <v>14371500</v>
       </c>
       <c r="BK24" s="4">
-        <v>-28275</v>
+        <v>690625</v>
       </c>
       <c r="BL24" s="4">
-        <v>100.38382570037163</v>
+        <v>90.62494697368199</v>
       </c>
       <c r="BM24" s="4">
         <v>5766300</v>
       </c>
       <c r="BN24" s="4">
-        <v>7394900</v>
+        <v>6676000</v>
       </c>
       <c r="BO24" s="4">
         <v>50857800</v>
@@ -13259,19 +13259,19 @@
         <v>33057570</v>
       </c>
       <c r="BR24" s="4">
-        <v>33729000</v>
+        <v>34090200</v>
       </c>
       <c r="BS24" s="4">
-        <v>671430</v>
+        <v>1032630</v>
       </c>
       <c r="BT24" s="4">
-        <v>96.22797008802695</v>
+        <v>94.1987828247163</v>
       </c>
       <c r="BU24" s="4">
         <v>12782600</v>
       </c>
       <c r="BV24" s="4">
-        <v>17128800</v>
+        <v>16767600</v>
       </c>
       <c r="CE24" s="4">
         <v>5382000</v>
@@ -13283,19 +13283,19 @@
         <v>3498300</v>
       </c>
       <c r="CH24" s="4">
-        <v>3407000</v>
+        <v>1955000</v>
       </c>
       <c r="CI24" s="4">
-        <v>-91300</v>
+        <v>-1543300</v>
       </c>
       <c r="CJ24" s="4">
-        <v>104.84684397727877</v>
+        <v>181.92918192918194</v>
       </c>
       <c r="CK24" s="4">
         <v>0</v>
       </c>
       <c r="CL24" s="4">
-        <v>1975000</v>
+        <v>3427000</v>
       </c>
       <c r="EY24" s="4">
         <v>1605920979</v>
@@ -13331,19 +13331,19 @@
         <v>1746424344</v>
       </c>
       <c r="FJ24" s="4">
-        <v>1748305079</v>
+        <v>1747933179</v>
       </c>
       <c r="FK24" s="4">
-        <v>1880735</v>
+        <v>1508835</v>
       </c>
       <c r="FL24" s="4">
-        <v>98.15474437572735</v>
+        <v>98.51962861867864</v>
       </c>
       <c r="FM24" s="4">
         <v>48294000</v>
       </c>
       <c r="FN24" s="4">
-        <v>100042000</v>
+        <v>100413900</v>
       </c>
       <c r="FO24" s="4">
         <v>183656000</v>
@@ -13427,19 +13427,19 @@
         <v>13478465</v>
       </c>
       <c r="HN24" s="4">
-        <v>18897300</v>
+        <v>19494600</v>
       </c>
       <c r="HO24" s="4">
-        <v>5418835</v>
+        <v>6016135</v>
       </c>
       <c r="HP24" s="4">
-        <v>25.336077110518783</v>
+        <v>17.106123413481114</v>
       </c>
       <c r="HQ24" s="4">
         <v>19770600</v>
       </c>
       <c r="HR24" s="4">
-        <v>1838800</v>
+        <v>1241500</v>
       </c>
       <c r="HS24" s="4">
         <v>12746900</v>
@@ -13451,19 +13451,19 @@
         <v>8285485</v>
       </c>
       <c r="HV24" s="4">
-        <v>8014300</v>
+        <v>8289800</v>
       </c>
       <c r="HW24" s="4">
-        <v>-271185</v>
+        <v>4315</v>
       </c>
       <c r="HX24" s="4">
-        <v>106.07845268821663</v>
+        <v>99.90328180633274</v>
       </c>
       <c r="HY24" s="4">
         <v>5766300</v>
       </c>
       <c r="HZ24" s="4">
-        <v>4732600</v>
+        <v>4457100</v>
       </c>
       <c r="IA24" s="4">
         <v>12498600</v>
@@ -13499,19 +13499,19 @@
         <v>2785250</v>
       </c>
       <c r="IL24" s="4">
-        <v>2778000</v>
+        <v>2158000</v>
       </c>
       <c r="IM24" s="4">
-        <v>-7250</v>
+        <v>-627250</v>
       </c>
       <c r="IN24" s="4">
-        <v>100.48341390231705</v>
+        <v>141.8236372728788</v>
       </c>
       <c r="IO24" s="4">
         <v>0</v>
       </c>
       <c r="IP24" s="4">
-        <v>1507000</v>
+        <v>2127000</v>
       </c>
       <c r="IQ24" s="4">
         <v>115350000</v>
@@ -13547,10 +13547,10 @@
         <v>1268880300</v>
       </c>
       <c r="JJ24" s="4">
-        <v>1203596600</v>
+        <v>1203343700</v>
       </c>
       <c r="JK24" s="4">
-        <v>-65283700</v>
+        <v>-65536600</v>
       </c>
       <c r="JL24" s="4">
         <v>0</v>
@@ -13559,7 +13559,7 @@
         <v>106539400</v>
       </c>
       <c r="JN24" s="4">
-        <v>65283700</v>
+        <v>65536600</v>
       </c>
       <c r="JO24" s="4">
         <v>4553398900</v>
@@ -13571,19 +13571,19 @@
         <v>3499278990</v>
       </c>
       <c r="JR24" s="4">
-        <v>3465626700</v>
+        <v>3465626600</v>
       </c>
       <c r="JS24" s="4">
-        <v>-33652290</v>
+        <v>-33652390</v>
       </c>
       <c r="JT24" s="4">
-        <v>103.19245369343228</v>
+        <v>103.19246318001905</v>
       </c>
       <c r="JU24" s="4">
         <v>1620985600</v>
       </c>
       <c r="JV24" s="4">
-        <v>1087772200</v>
+        <v>1087772300</v>
       </c>
       <c r="JW24" s="4">
         <v>292480000</v>
@@ -13667,19 +13667,19 @@
         <v>43241185</v>
       </c>
       <c r="LV24" s="4">
-        <v>48610800</v>
+        <v>49208100</v>
       </c>
       <c r="LW24" s="4">
-        <v>5369615</v>
+        <v>5966915</v>
       </c>
       <c r="LX24" s="4">
-        <v>76.93832363091543</v>
+        <v>74.3730113514961</v>
       </c>
       <c r="LY24" s="4">
         <v>19770600</v>
       </c>
       <c r="LZ24" s="4">
-        <v>17914100</v>
+        <v>17316800</v>
       </c>
       <c r="MA24" s="4">
         <v>33794400</v>
@@ -13691,19 +13691,19 @@
         <v>21966360</v>
       </c>
       <c r="MD24" s="4">
-        <v>21666900</v>
+        <v>22661300</v>
       </c>
       <c r="ME24" s="4">
-        <v>-299460</v>
+        <v>694940</v>
       </c>
       <c r="MF24" s="4">
-        <v>102.53178041332292</v>
+        <v>94.12463941616701</v>
       </c>
       <c r="MG24" s="4">
         <v>5766300</v>
       </c>
       <c r="MH24" s="4">
-        <v>12127500</v>
+        <v>11133100</v>
       </c>
       <c r="MQ24" s="4">
         <v>12498600</v>
@@ -13739,19 +13739,19 @@
         <v>6283550</v>
       </c>
       <c r="NB24" s="4">
-        <v>6185000</v>
+        <v>4113000</v>
       </c>
       <c r="NC24" s="4">
-        <v>-98550</v>
+        <v>-2170550</v>
       </c>
       <c r="ND24" s="4">
-        <v>102.91270744358569</v>
+        <v>164.15197505504736</v>
       </c>
       <c r="NE24" s="4">
         <v>0</v>
       </c>
       <c r="NF24" s="4">
-        <v>3482000</v>
+        <v>5554000</v>
       </c>
       <c r="NO24" s="4">
         <v>115350000</v>
@@ -13811,10 +13811,10 @@
         <v>2845914479</v>
       </c>
       <c r="QD24" s="4">
-        <v>2781090979</v>
+        <v>2780840479</v>
       </c>
       <c r="QE24" s="4">
-        <v>-64823500</v>
+        <v>-65074000</v>
       </c>
       <c r="QF24" s="4">
         <v>0</v>
@@ -13823,7 +13823,7 @@
         <v>713152751</v>
       </c>
       <c r="QH24" s="4">
-        <v>64823500</v>
+        <v>65074000</v>
       </c>
       <c r="QI24" s="4">
         <v>6401745979</v>
@@ -13835,19 +13835,19 @@
         <v>5245703334</v>
       </c>
       <c r="QL24" s="4">
-        <v>5213931779</v>
+        <v>5213559779</v>
       </c>
       <c r="QM24" s="4">
-        <v>-31771555</v>
+        <v>-32143555</v>
       </c>
       <c r="QN24" s="4">
-        <v>-102.74830302648567</v>
+        <v>-102.78048177020321</v>
       </c>
       <c r="QO24" s="4">
         <v>1633768200</v>
       </c>
       <c r="QP24" s="4">
-        <v>-1187814200</v>
+        <v>-1188186200</v>
       </c>
     </row>
     <row r="25">
@@ -13939,19 +13939,19 @@
         <v>13542945</v>
       </c>
       <c r="BB25" s="4">
-        <v>12174100</v>
+        <v>13769400</v>
       </c>
       <c r="BC25" s="4">
-        <v>-1368845</v>
+        <v>226455</v>
       </c>
       <c r="BD25" s="4">
-        <v>118.77095944999935</v>
+        <v>96.89462457601145</v>
       </c>
       <c r="BE25" s="4">
         <v>10733500</v>
       </c>
       <c r="BF25" s="4">
-        <v>8661200</v>
+        <v>7065900</v>
       </c>
       <c r="BG25" s="4">
         <v>9379300</v>
@@ -13963,19 +13963,19 @@
         <v>6096545</v>
       </c>
       <c r="BJ25" s="4">
-        <v>5990100</v>
+        <v>6726900</v>
       </c>
       <c r="BK25" s="4">
-        <v>-106445</v>
+        <v>630355</v>
       </c>
       <c r="BL25" s="4">
-        <v>103.2425508452504</v>
+        <v>80.79798827509211</v>
       </c>
       <c r="BM25" s="4">
         <v>6592100</v>
       </c>
       <c r="BN25" s="4">
-        <v>3389200</v>
+        <v>2652400</v>
       </c>
       <c r="BO25" s="4">
         <v>12128100</v>
@@ -14035,19 +14035,19 @@
         <v>5122000</v>
       </c>
       <c r="DN25" s="4">
-        <v>5122000</v>
+        <v>7880000</v>
       </c>
       <c r="DO25" s="4">
-        <v>0</v>
+        <v>2758000</v>
       </c>
       <c r="DP25" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DQ25" s="4">
         <v>6411000</v>
       </c>
       <c r="DR25" s="4">
-        <v>2758000</v>
+        <v>0</v>
       </c>
       <c r="EY25" s="4">
         <v>2540603894</v>
@@ -14059,10 +14059,10 @@
         <v>2540603894</v>
       </c>
       <c r="FB25" s="4">
-        <v>2534620594</v>
+        <v>2529491594</v>
       </c>
       <c r="FC25" s="4">
-        <v>-5983300</v>
+        <v>-11112300</v>
       </c>
       <c r="FD25" s="4">
         <v>0</v>
@@ -14071,7 +14071,7 @@
         <v>921120101</v>
       </c>
       <c r="FF25" s="4">
-        <v>5983300</v>
+        <v>11112300</v>
       </c>
       <c r="FG25" s="4">
         <v>2717175594</v>
@@ -14083,19 +14083,19 @@
         <v>2638393999</v>
       </c>
       <c r="FJ25" s="4">
-        <v>2628026194</v>
+        <v>2627987294</v>
       </c>
       <c r="FK25" s="4">
-        <v>-10367805</v>
+        <v>-10406705</v>
       </c>
       <c r="FL25" s="4">
-        <v>113.16018671619939</v>
+        <v>113.20956373122428</v>
       </c>
       <c r="FM25" s="4">
         <v>113096460</v>
       </c>
       <c r="FN25" s="4">
-        <v>89149400</v>
+        <v>89188300</v>
       </c>
       <c r="FO25" s="4">
         <v>213383000</v>
@@ -14179,19 +14179,19 @@
         <v>35055020</v>
       </c>
       <c r="HN25" s="4">
-        <v>35452000</v>
+        <v>35450400</v>
       </c>
       <c r="HO25" s="4">
-        <v>396980</v>
+        <v>395380</v>
       </c>
       <c r="HP25" s="4">
-        <v>97.89688161230953</v>
+        <v>97.90535808321563</v>
       </c>
       <c r="HQ25" s="4">
         <v>10733500</v>
       </c>
       <c r="HR25" s="4">
-        <v>18478800</v>
+        <v>18480400</v>
       </c>
       <c r="HS25" s="4">
         <v>6059000</v>
@@ -14299,19 +14299,19 @@
         <v>2266440620</v>
       </c>
       <c r="JR25" s="4">
-        <v>2247819500</v>
+        <v>2247817900</v>
       </c>
       <c r="JS25" s="4">
-        <v>-18621120</v>
+        <v>-18622720</v>
       </c>
       <c r="JT25" s="4">
-        <v>104.85481938811681</v>
+        <v>104.85523653332724</v>
       </c>
       <c r="JU25" s="4">
         <v>105267860</v>
       </c>
       <c r="JV25" s="4">
-        <v>402180600</v>
+        <v>402182200</v>
       </c>
       <c r="JW25" s="4">
         <v>286093000</v>
@@ -14395,19 +14395,19 @@
         <v>48597965</v>
       </c>
       <c r="LV25" s="4">
-        <v>47626100</v>
+        <v>49219800</v>
       </c>
       <c r="LW25" s="4">
-        <v>-971865</v>
+        <v>621835</v>
       </c>
       <c r="LX25" s="4">
-        <v>103.71392535234169</v>
+        <v>97.62369385514098</v>
       </c>
       <c r="LY25" s="4">
         <v>10733500</v>
       </c>
       <c r="LZ25" s="4">
-        <v>27140000</v>
+        <v>25546300</v>
       </c>
       <c r="MA25" s="4">
         <v>15438300</v>
@@ -14419,19 +14419,19 @@
         <v>10034895</v>
       </c>
       <c r="MD25" s="4">
-        <v>9722500</v>
+        <v>10459300</v>
       </c>
       <c r="ME25" s="4">
-        <v>-312395</v>
+        <v>424405</v>
       </c>
       <c r="MF25" s="4">
-        <v>105.78144706902405</v>
+        <v>92.14560078320984</v>
       </c>
       <c r="MG25" s="4">
         <v>6592100</v>
       </c>
       <c r="MH25" s="4">
-        <v>5715800</v>
+        <v>4979000</v>
       </c>
       <c r="MY25" s="4">
         <v>260661000</v>
@@ -14491,10 +14491,10 @@
         <v>4194079694</v>
       </c>
       <c r="QD25" s="4">
-        <v>4168076394</v>
+        <v>4162947394</v>
       </c>
       <c r="QE25" s="4">
-        <v>-26003300</v>
+        <v>-31132300</v>
       </c>
       <c r="QF25" s="4">
         <v>0</v>
@@ -14503,7 +14503,7 @@
         <v>924120101</v>
       </c>
       <c r="QH25" s="4">
-        <v>26003300</v>
+        <v>31132300</v>
       </c>
       <c r="QI25" s="4">
         <v>5367175694</v>
@@ -14515,19 +14515,19 @@
         <v>4904834619</v>
       </c>
       <c r="QL25" s="4">
-        <v>4875845694</v>
+        <v>4875805194</v>
       </c>
       <c r="QM25" s="4">
-        <v>-28988925</v>
+        <v>-29029425</v>
       </c>
       <c r="QN25" s="4">
-        <v>-106.27003019361842</v>
+        <v>-106.27878996042045</v>
       </c>
       <c r="QO25" s="4">
         <v>115346460</v>
       </c>
       <c r="QP25" s="4">
-        <v>-491330000</v>
+        <v>-491370500</v>
       </c>
     </row>
     <row r="26">
@@ -14811,19 +14811,19 @@
         <v>62400000</v>
       </c>
       <c r="GH26" s="4">
-        <v>24200000</v>
+        <v>83700000</v>
       </c>
       <c r="GI26" s="4">
-        <v>-38200000</v>
+        <v>21300000</v>
       </c>
       <c r="GJ26" s="4">
-        <v>161.21794871794873</v>
+        <v>65.86538461538461</v>
       </c>
       <c r="GK26" s="4">
         <v>0</v>
       </c>
       <c r="GL26" s="4">
-        <v>100600000</v>
+        <v>41100000</v>
       </c>
       <c r="GU26" s="4">
         <v>241562000</v>
@@ -14835,19 +14835,19 @@
         <v>120781000</v>
       </c>
       <c r="GX26" s="4">
-        <v>100267000</v>
+        <v>118412000</v>
       </c>
       <c r="GY26" s="4">
-        <v>-20514000</v>
+        <v>-2369000</v>
       </c>
       <c r="GZ26" s="4">
-        <v>116.98445947624212</v>
+        <v>101.96140121376706</v>
       </c>
       <c r="HA26" s="4">
         <v>5839600</v>
       </c>
       <c r="HB26" s="4">
-        <v>141295000</v>
+        <v>123150000</v>
       </c>
       <c r="HK26" s="4">
         <v>30836100</v>
@@ -14859,19 +14859,19 @@
         <v>20043465</v>
       </c>
       <c r="HN26" s="4">
-        <v>13516200</v>
+        <v>13550000</v>
       </c>
       <c r="HO26" s="4">
-        <v>-6527265</v>
+        <v>-6493465</v>
       </c>
       <c r="HP26" s="4">
-        <v>160.47888212656133</v>
+        <v>160.16570559460223</v>
       </c>
       <c r="HQ26" s="4">
         <v>1988300</v>
       </c>
       <c r="HR26" s="4">
-        <v>17319900</v>
+        <v>17286100</v>
       </c>
       <c r="HS26" s="4">
         <v>6792400</v>
@@ -14907,19 +14907,19 @@
         <v>12324000</v>
       </c>
       <c r="IL26" s="4">
-        <v>8690000</v>
+        <v>31010000</v>
       </c>
       <c r="IM26" s="4">
-        <v>-3634000</v>
+        <v>18686000</v>
       </c>
       <c r="IN26" s="4">
-        <v>154.76190476190476</v>
+        <v>-181.585292344786</v>
       </c>
       <c r="IO26" s="4">
         <v>2205000</v>
       </c>
       <c r="IP26" s="4">
-        <v>10270000</v>
+        <v>-12050000</v>
       </c>
       <c r="JG26" s="4">
         <v>27048800</v>
@@ -14931,10 +14931,10 @@
         <v>27048800</v>
       </c>
       <c r="JJ26" s="4">
-        <v>12333800</v>
+        <v>12335000</v>
       </c>
       <c r="JK26" s="4">
-        <v>-14715000</v>
+        <v>-14713800</v>
       </c>
       <c r="JL26" s="4">
         <v>0</v>
@@ -14943,7 +14943,7 @@
         <v>0</v>
       </c>
       <c r="JN26" s="4">
-        <v>14715000</v>
+        <v>14713800</v>
       </c>
       <c r="JO26" s="4">
         <v>449999300</v>
@@ -14955,19 +14955,19 @@
         <v>247012325</v>
       </c>
       <c r="JR26" s="4">
-        <v>162128500</v>
+        <v>262128500</v>
       </c>
       <c r="JS26" s="4">
-        <v>-84883825</v>
+        <v>15116175</v>
       </c>
       <c r="JT26" s="4">
-        <v>141.81737522813964</v>
+        <v>92.55313056416551</v>
       </c>
       <c r="JU26" s="4">
         <v>11174200</v>
       </c>
       <c r="JV26" s="4">
-        <v>287870800</v>
+        <v>187870800</v>
       </c>
       <c r="KM26" s="4">
         <v>124800000</v>
@@ -14979,19 +14979,19 @@
         <v>62400000</v>
       </c>
       <c r="KP26" s="4">
-        <v>24200000</v>
+        <v>83700000</v>
       </c>
       <c r="KQ26" s="4">
-        <v>-38200000</v>
+        <v>21300000</v>
       </c>
       <c r="KR26" s="4">
-        <v>161.21794871794873</v>
+        <v>65.86538461538461</v>
       </c>
       <c r="KS26" s="4">
         <v>0</v>
       </c>
       <c r="KT26" s="4">
-        <v>100600000</v>
+        <v>41100000</v>
       </c>
       <c r="LC26" s="4">
         <v>241562000</v>
@@ -15003,19 +15003,19 @@
         <v>120781000</v>
       </c>
       <c r="LF26" s="4">
-        <v>100267000</v>
+        <v>118412000</v>
       </c>
       <c r="LG26" s="4">
-        <v>-20514000</v>
+        <v>-2369000</v>
       </c>
       <c r="LH26" s="4">
-        <v>116.98445947624212</v>
+        <v>101.96140121376706</v>
       </c>
       <c r="LI26" s="4">
         <v>5839600</v>
       </c>
       <c r="LJ26" s="4">
-        <v>141295000</v>
+        <v>123150000</v>
       </c>
       <c r="LS26" s="4">
         <v>58814200</v>
@@ -15027,19 +15027,19 @@
         <v>38229230</v>
       </c>
       <c r="LV26" s="4">
-        <v>31768200</v>
+        <v>31802000</v>
       </c>
       <c r="LW26" s="4">
-        <v>-6461030</v>
+        <v>-6427230</v>
       </c>
       <c r="LX26" s="4">
-        <v>131.38712371210644</v>
+        <v>131.22292624181625</v>
       </c>
       <c r="LY26" s="4">
         <v>1988300</v>
       </c>
       <c r="LZ26" s="4">
-        <v>27046000</v>
+        <v>27012200</v>
       </c>
       <c r="MA26" s="4">
         <v>13703500</v>
@@ -15075,19 +15075,19 @@
         <v>23461750</v>
       </c>
       <c r="NB26" s="4">
-        <v>19764000</v>
+        <v>42084000</v>
       </c>
       <c r="NC26" s="4">
-        <v>-3697750</v>
+        <v>18622250</v>
       </c>
       <c r="ND26" s="4">
-        <v>129.26998199196564</v>
+        <v>-47.40664516256704</v>
       </c>
       <c r="NE26" s="4">
         <v>2205000</v>
       </c>
       <c r="NF26" s="4">
-        <v>16331000</v>
+        <v>-5989000</v>
       </c>
       <c r="QA26" s="4">
         <v>3830195209</v>
@@ -15123,19 +15123,19 @@
         <v>4160491509</v>
       </c>
       <c r="QL26" s="4">
-        <v>4076507709</v>
+        <v>4176507709</v>
       </c>
       <c r="QM26" s="4">
-        <v>-83983800</v>
+        <v>16016200</v>
       </c>
       <c r="QN26" s="4">
-        <v>-131.63962150206433</v>
+        <v>-93.96613982814111</v>
       </c>
       <c r="QO26" s="4">
         <v>16769200</v>
       </c>
       <c r="QP26" s="4">
-        <v>-349422500</v>
+        <v>-249422500</v>
       </c>
     </row>
     <row r="27">
@@ -15155,19 +15155,19 @@
         <v>46674000</v>
       </c>
       <c r="F27" s="4">
-        <v>60246000</v>
+        <v>53788000</v>
       </c>
       <c r="G27" s="4">
-        <v>13572000</v>
+        <v>7114000</v>
       </c>
       <c r="H27" s="4">
-        <v>70.92171230235249</v>
+        <v>84.75810943994514</v>
       </c>
       <c r="I27" s="4">
         <v>29439600</v>
       </c>
       <c r="J27" s="4">
-        <v>33102000</v>
+        <v>39560000</v>
       </c>
       <c r="S27" s="4">
         <v>11600000</v>
@@ -15347,10 +15347,10 @@
         <v>1778928165</v>
       </c>
       <c r="FB27" s="4">
-        <v>1778928165</v>
+        <v>1778137750</v>
       </c>
       <c r="FC27" s="4">
-        <v>0</v>
+        <v>-790415</v>
       </c>
       <c r="FD27" s="4">
         <v>0</v>
@@ -15359,7 +15359,7 @@
         <v>685235839</v>
       </c>
       <c r="FF27" s="4">
-        <v>0</v>
+        <v>790415</v>
       </c>
       <c r="FG27" s="4">
         <v>1976660365</v>
@@ -15371,19 +15371,19 @@
         <v>1891711895</v>
       </c>
       <c r="FJ27" s="4">
-        <v>1904955665</v>
+        <v>1897707250</v>
       </c>
       <c r="FK27" s="4">
-        <v>13243770</v>
+        <v>5995355</v>
       </c>
       <c r="FL27" s="4">
-        <v>84.40964269279952</v>
+        <v>92.9423625875781</v>
       </c>
       <c r="FM27" s="4">
         <v>93069900</v>
       </c>
       <c r="FN27" s="4">
-        <v>71704700</v>
+        <v>78953115</v>
       </c>
       <c r="FO27" s="4">
         <v>176990000</v>
@@ -15395,19 +15395,19 @@
         <v>88495000</v>
       </c>
       <c r="FR27" s="4">
-        <v>44280000</v>
+        <v>51218000</v>
       </c>
       <c r="FS27" s="4">
-        <v>-44215000</v>
+        <v>-37277000</v>
       </c>
       <c r="FT27" s="4">
-        <v>149.96327476128596</v>
+        <v>142.1232838013447</v>
       </c>
       <c r="FU27" s="4">
         <v>29439600</v>
       </c>
       <c r="FV27" s="4">
-        <v>132710000</v>
+        <v>125772000</v>
       </c>
       <c r="GE27" s="4">
         <v>109100000</v>
@@ -15491,19 +15491,19 @@
         <v>17732000</v>
       </c>
       <c r="IL27" s="4">
-        <v>2542000</v>
+        <v>2852000</v>
       </c>
       <c r="IM27" s="4">
-        <v>-15190000</v>
+        <v>-14880000</v>
       </c>
       <c r="IN27" s="4">
-        <v>259.09090909090907</v>
+        <v>255.84415584415586</v>
       </c>
       <c r="IO27" s="4">
         <v>6696000</v>
       </c>
       <c r="IP27" s="4">
-        <v>24738000</v>
+        <v>24428000</v>
       </c>
       <c r="JG27" s="4">
         <v>85115000</v>
@@ -15539,19 +15539,19 @@
         <v>247359700</v>
       </c>
       <c r="JR27" s="4">
-        <v>85522000</v>
+        <v>92770000</v>
       </c>
       <c r="JS27" s="4">
-        <v>-161837700</v>
+        <v>-154589700</v>
       </c>
       <c r="JT27" s="4">
-        <v>205.51194295598023</v>
+        <v>200.786526303711</v>
       </c>
       <c r="JU27" s="4">
         <v>80682700</v>
       </c>
       <c r="JV27" s="4">
-        <v>315221000</v>
+        <v>307973000</v>
       </c>
       <c r="JW27" s="4">
         <v>270338000</v>
@@ -15563,19 +15563,19 @@
         <v>135169000</v>
       </c>
       <c r="JZ27" s="4">
-        <v>104526000</v>
+        <v>105006000</v>
       </c>
       <c r="KA27" s="4">
-        <v>-30643000</v>
+        <v>-30163000</v>
       </c>
       <c r="KB27" s="4">
-        <v>122.67013886320089</v>
+        <v>122.31502785401977</v>
       </c>
       <c r="KC27" s="4">
         <v>29439600</v>
       </c>
       <c r="KD27" s="4">
-        <v>165812000</v>
+        <v>165332000</v>
       </c>
       <c r="KM27" s="4">
         <v>120700000</v>
@@ -15683,19 +15683,19 @@
         <v>24542700</v>
       </c>
       <c r="NB27" s="4">
-        <v>11160000</v>
+        <v>11470000</v>
       </c>
       <c r="NC27" s="4">
-        <v>-13382700</v>
+        <v>-13072700</v>
       </c>
       <c r="ND27" s="4">
-        <v>201.2667135819845</v>
+        <v>198.9209476894206</v>
       </c>
       <c r="NE27" s="4">
         <v>6696000</v>
       </c>
       <c r="NF27" s="4">
-        <v>26598000</v>
+        <v>26288000</v>
       </c>
       <c r="QA27" s="4">
         <v>1844903165</v>
@@ -15707,10 +15707,10 @@
         <v>1844903165</v>
       </c>
       <c r="QD27" s="4">
-        <v>1778928165</v>
+        <v>1778137750</v>
       </c>
       <c r="QE27" s="4">
-        <v>-65975000</v>
+        <v>-66765415</v>
       </c>
       <c r="QF27" s="4">
         <v>0</v>
@@ -15719,7 +15719,7 @@
         <v>685235839</v>
       </c>
       <c r="QH27" s="4">
-        <v>65975000</v>
+        <v>66765415</v>
       </c>
       <c r="QI27" s="4">
         <v>2377403365</v>
@@ -15731,19 +15731,19 @@
         <v>2139071595</v>
       </c>
       <c r="QL27" s="4">
-        <v>1990477665</v>
+        <v>1990477250</v>
       </c>
       <c r="QM27" s="4">
-        <v>-148593930</v>
+        <v>-148594345</v>
       </c>
       <c r="QN27" s="4">
-        <v>-162.3475124613055</v>
+        <v>-162.3476865883218</v>
       </c>
       <c r="QO27" s="4">
         <v>93069900</v>
       </c>
       <c r="QP27" s="4">
-        <v>-386925700</v>
+        <v>-386926115</v>
       </c>
     </row>
     <row r="28">
@@ -16299,19 +16299,19 @@
         <v>5921695</v>
       </c>
       <c r="BJ29" s="4">
-        <v>5894100</v>
+        <v>6086300</v>
       </c>
       <c r="BK29" s="4">
-        <v>-27595</v>
+        <v>164605</v>
       </c>
       <c r="BL29" s="4">
-        <v>100.86542547603105</v>
+        <v>94.83771116209125</v>
       </c>
       <c r="BM29" s="4">
         <v>2024300</v>
       </c>
       <c r="BN29" s="4">
-        <v>3216200</v>
+        <v>3024000</v>
       </c>
       <c r="BO29" s="4">
         <v>26221200</v>
@@ -16323,19 +16323,19 @@
         <v>17043780</v>
       </c>
       <c r="BR29" s="4">
-        <v>20023800</v>
+        <v>19594800</v>
       </c>
       <c r="BS29" s="4">
-        <v>2980020</v>
+        <v>2551020</v>
       </c>
       <c r="BT29" s="4">
-        <v>67.5287825990311</v>
+        <v>72.20329896637617</v>
       </c>
       <c r="BU29" s="4">
         <v>2499600</v>
       </c>
       <c r="BV29" s="4">
-        <v>6197400</v>
+        <v>6626400</v>
       </c>
       <c r="CE29" s="4">
         <v>19840000</v>
@@ -16395,19 +16395,19 @@
         <v>0</v>
       </c>
       <c r="DN29" s="4">
-        <v>25441000</v>
+        <v>0</v>
       </c>
       <c r="DO29" s="4">
-        <v>25441000</v>
+        <v>0</v>
       </c>
       <c r="DP29" s="4">
-        <v>-Infinity</v>
+        <v>NaN</v>
       </c>
       <c r="DQ29" s="4">
         <v>0</v>
       </c>
       <c r="DR29" s="4">
-        <v>-25441000</v>
+        <v>0</v>
       </c>
       <c r="DS29" s="4">
         <v>34560000</v>
@@ -16491,19 +16491,19 @@
         <v>3585880033</v>
       </c>
       <c r="FJ29" s="4">
-        <v>3585879818</v>
+        <v>3560202018</v>
       </c>
       <c r="FK29" s="4">
-        <v>-215</v>
+        <v>-25678015</v>
       </c>
       <c r="FL29" s="4">
-        <v>100.00015091957226</v>
+        <v>118.02472111730182</v>
       </c>
       <c r="FM29" s="4">
         <v>26537100</v>
       </c>
       <c r="FN29" s="4">
-        <v>142460200</v>
+        <v>168138000</v>
       </c>
       <c r="KM29" s="4">
         <v>23100000</v>
@@ -16611,19 +16611,19 @@
         <v>5921695</v>
       </c>
       <c r="MD29" s="4">
-        <v>5894100</v>
+        <v>6086300</v>
       </c>
       <c r="ME29" s="4">
-        <v>-27595</v>
+        <v>164605</v>
       </c>
       <c r="MF29" s="4">
-        <v>100.86542547603105</v>
+        <v>94.83771116209125</v>
       </c>
       <c r="MG29" s="4">
         <v>2024300</v>
       </c>
       <c r="MH29" s="4">
-        <v>3216200</v>
+        <v>3024000</v>
       </c>
       <c r="MY29" s="4">
         <v>19840000</v>
@@ -16707,19 +16707,19 @@
         <v>3585880033</v>
       </c>
       <c r="QL29" s="4">
-        <v>3585879818</v>
+        <v>3560202018</v>
       </c>
       <c r="QM29" s="4">
-        <v>-215</v>
+        <v>-25678015</v>
       </c>
       <c r="QN29" s="4">
-        <v>-100.00015091957226</v>
+        <v>-118.02472111730182</v>
       </c>
       <c r="QO29" s="4">
         <v>26537100</v>
       </c>
       <c r="QP29" s="4">
-        <v>-142460200</v>
+        <v>-168138000</v>
       </c>
     </row>
     <row r="30">
@@ -17403,19 +17403,19 @@
         <v>212254120</v>
       </c>
       <c r="AT32" s="4">
-        <v>302247800</v>
+        <v>576496000</v>
       </c>
       <c r="AU32" s="4">
-        <v>89993680</v>
+        <v>364241880</v>
       </c>
       <c r="AV32" s="4">
-        <v>21.25895129856608</v>
+        <v>-218.6977975806951</v>
       </c>
       <c r="AW32" s="4">
         <v>133200000</v>
       </c>
       <c r="AX32" s="4">
-        <v>24297000</v>
+        <v>-249951200</v>
       </c>
       <c r="AY32" s="4">
         <v>283683000</v>
@@ -17427,19 +17427,19 @@
         <v>184393950</v>
       </c>
       <c r="BB32" s="4">
-        <v>184395000</v>
+        <v>283683000</v>
       </c>
       <c r="BC32" s="4">
-        <v>1050</v>
+        <v>99289050</v>
       </c>
       <c r="BD32" s="4">
-        <v>99.99894248157274</v>
+        <v>0</v>
       </c>
       <c r="BE32" s="4">
         <v>72393600</v>
       </c>
       <c r="BF32" s="4">
-        <v>99288000</v>
+        <v>0</v>
       </c>
       <c r="BG32" s="4">
         <v>105836000</v>
@@ -17451,19 +17451,19 @@
         <v>68793400</v>
       </c>
       <c r="BJ32" s="4">
-        <v>68806000</v>
+        <v>105836000</v>
       </c>
       <c r="BK32" s="4">
-        <v>12600</v>
+        <v>37042600</v>
       </c>
       <c r="BL32" s="4">
-        <v>99.96598510903662</v>
+        <v>0</v>
       </c>
       <c r="BM32" s="4">
         <v>36594400</v>
       </c>
       <c r="BN32" s="4">
-        <v>37030000</v>
+        <v>0</v>
       </c>
       <c r="BO32" s="4">
         <v>62959500</v>
@@ -17475,19 +17475,19 @@
         <v>40923675</v>
       </c>
       <c r="BR32" s="4">
-        <v>40911000</v>
+        <v>62966700</v>
       </c>
       <c r="BS32" s="4">
-        <v>-12675</v>
+        <v>22043025</v>
       </c>
       <c r="BT32" s="4">
-        <v>100.05751997032107</v>
+        <v>-0.03267406598119199</v>
       </c>
       <c r="BU32" s="4">
         <v>0</v>
       </c>
       <c r="BV32" s="4">
-        <v>22048500</v>
+        <v>-7200</v>
       </c>
       <c r="BW32" s="4">
         <v>1561307400</v>
@@ -17499,19 +17499,19 @@
         <v>1014849810</v>
       </c>
       <c r="BZ32" s="4">
-        <v>1076981900</v>
+        <v>1434278900</v>
       </c>
       <c r="CA32" s="4">
-        <v>62132090</v>
+        <v>419429090</v>
       </c>
       <c r="CB32" s="4">
-        <v>88.6300252504499</v>
+        <v>23.24581126231589</v>
       </c>
       <c r="CC32" s="4">
         <v>238775520</v>
       </c>
       <c r="CD32" s="4">
-        <v>484325500</v>
+        <v>127028500</v>
       </c>
       <c r="CE32" s="4">
         <v>291926000</v>
@@ -17523,19 +17523,19 @@
         <v>189751900</v>
       </c>
       <c r="CH32" s="4">
-        <v>189738000</v>
+        <v>291926000</v>
       </c>
       <c r="CI32" s="4">
-        <v>-13900</v>
+        <v>102174100</v>
       </c>
       <c r="CJ32" s="4">
-        <v>100.01360423042631</v>
+        <v>0</v>
       </c>
       <c r="CK32" s="4">
         <v>19690000</v>
       </c>
       <c r="CL32" s="4">
-        <v>102188000</v>
+        <v>0</v>
       </c>
       <c r="CM32" s="4">
         <v>1408750000</v>
@@ -17547,19 +17547,19 @@
         <v>915687500</v>
       </c>
       <c r="CP32" s="4">
-        <v>915670000</v>
+        <v>1250060000</v>
       </c>
       <c r="CQ32" s="4">
-        <v>-17500</v>
+        <v>334372500</v>
       </c>
       <c r="CR32" s="4">
-        <v>100.00354924578528</v>
+        <v>32.184560780834076</v>
       </c>
       <c r="CS32" s="4">
         <v>169620000</v>
       </c>
       <c r="CT32" s="4">
-        <v>493080000</v>
+        <v>158690000</v>
       </c>
       <c r="DC32" s="4">
         <v>849890000</v>
@@ -17571,19 +17571,19 @@
         <v>552428500</v>
       </c>
       <c r="DF32" s="4">
-        <v>552410000</v>
+        <v>849890000</v>
       </c>
       <c r="DG32" s="4">
-        <v>-18500</v>
+        <v>297461500</v>
       </c>
       <c r="DH32" s="4">
-        <v>100.00621929224454</v>
+        <v>0</v>
       </c>
       <c r="DI32" s="4">
         <v>424827600</v>
       </c>
       <c r="DJ32" s="4">
-        <v>297480000</v>
+        <v>0</v>
       </c>
       <c r="DK32" s="4">
         <v>768500000</v>
@@ -17595,19 +17595,19 @@
         <v>499525000</v>
       </c>
       <c r="DN32" s="4">
-        <v>486240000</v>
+        <v>611940000</v>
       </c>
       <c r="DO32" s="4">
-        <v>-13285000</v>
+        <v>112415000</v>
       </c>
       <c r="DP32" s="4">
-        <v>104.9391207361279</v>
+        <v>58.206152988195925</v>
       </c>
       <c r="DQ32" s="4">
         <v>94754000</v>
       </c>
       <c r="DR32" s="4">
-        <v>282260000</v>
+        <v>156560000</v>
       </c>
       <c r="DS32" s="4">
         <v>313590000</v>
@@ -17715,10 +17715,10 @@
         <v>5723934800</v>
       </c>
       <c r="FB32" s="4">
-        <v>5246634800</v>
+        <v>6019934800</v>
       </c>
       <c r="FC32" s="4">
-        <v>-477300000</v>
+        <v>296000000</v>
       </c>
       <c r="FD32" s="4">
         <v>0</v>
@@ -17727,7 +17727,7 @@
         <v>643485000</v>
       </c>
       <c r="FF32" s="4">
-        <v>477300000</v>
+        <v>-296000000</v>
       </c>
       <c r="FG32" s="4">
         <v>13513706100</v>
@@ -17739,19 +17739,19 @@
         <v>10663336695</v>
       </c>
       <c r="FJ32" s="4">
-        <v>11090729100</v>
+        <v>13513706000</v>
       </c>
       <c r="FK32" s="4">
-        <v>427392405</v>
+        <v>2850369305</v>
       </c>
       <c r="FL32" s="4">
-        <v>85.00571875875856</v>
+        <v>0.0000035083171965214102</v>
       </c>
       <c r="FM32" s="4">
         <v>1263075924</v>
       </c>
       <c r="FN32" s="4">
-        <v>2422977000</v>
+        <v>100</v>
       </c>
       <c r="JW32" s="4">
         <v>160863000</v>
@@ -17787,19 +17787,19 @@
         <v>212254120</v>
       </c>
       <c r="LN32" s="4">
-        <v>302247800</v>
+        <v>576496000</v>
       </c>
       <c r="LO32" s="4">
-        <v>89993680</v>
+        <v>364241880</v>
       </c>
       <c r="LP32" s="4">
-        <v>21.25895129856608</v>
+        <v>-218.6977975806951</v>
       </c>
       <c r="LQ32" s="4">
         <v>133200000</v>
       </c>
       <c r="LR32" s="4">
-        <v>24297000</v>
+        <v>-249951200</v>
       </c>
       <c r="LS32" s="4">
         <v>283683000</v>
@@ -17811,19 +17811,19 @@
         <v>184393950</v>
       </c>
       <c r="LV32" s="4">
-        <v>184395000</v>
+        <v>283683000</v>
       </c>
       <c r="LW32" s="4">
-        <v>1050</v>
+        <v>99289050</v>
       </c>
       <c r="LX32" s="4">
-        <v>99.99894248157274</v>
+        <v>0</v>
       </c>
       <c r="LY32" s="4">
         <v>72393600</v>
       </c>
       <c r="LZ32" s="4">
-        <v>99288000</v>
+        <v>0</v>
       </c>
       <c r="MA32" s="4">
         <v>105836000</v>
@@ -17835,19 +17835,19 @@
         <v>68793400</v>
       </c>
       <c r="MD32" s="4">
-        <v>68806000</v>
+        <v>105836000</v>
       </c>
       <c r="ME32" s="4">
-        <v>12600</v>
+        <v>37042600</v>
       </c>
       <c r="MF32" s="4">
-        <v>99.96598510903662</v>
+        <v>0</v>
       </c>
       <c r="MG32" s="4">
         <v>36594400</v>
       </c>
       <c r="MH32" s="4">
-        <v>37030000</v>
+        <v>0</v>
       </c>
       <c r="MQ32" s="4">
         <v>1561307400</v>
@@ -17859,19 +17859,19 @@
         <v>1014849810</v>
       </c>
       <c r="MT32" s="4">
-        <v>1076981900</v>
+        <v>1434278900</v>
       </c>
       <c r="MU32" s="4">
-        <v>62132090</v>
+        <v>419429090</v>
       </c>
       <c r="MV32" s="4">
-        <v>88.6300252504499</v>
+        <v>23.24581126231589</v>
       </c>
       <c r="MW32" s="4">
         <v>238775520</v>
       </c>
       <c r="MX32" s="4">
-        <v>484325500</v>
+        <v>127028500</v>
       </c>
       <c r="MY32" s="4">
         <v>291926000</v>
@@ -17883,19 +17883,19 @@
         <v>189751900</v>
       </c>
       <c r="NB32" s="4">
-        <v>189738000</v>
+        <v>291926000</v>
       </c>
       <c r="NC32" s="4">
-        <v>-13900</v>
+        <v>102174100</v>
       </c>
       <c r="ND32" s="4">
-        <v>100.01360423042631</v>
+        <v>0</v>
       </c>
       <c r="NE32" s="4">
         <v>19690000</v>
       </c>
       <c r="NF32" s="4">
-        <v>102188000</v>
+        <v>0</v>
       </c>
       <c r="QA32" s="4">
         <v>5723934800</v>
@@ -17907,10 +17907,10 @@
         <v>5723934800</v>
       </c>
       <c r="QD32" s="4">
-        <v>5246634800</v>
+        <v>6019934800</v>
       </c>
       <c r="QE32" s="4">
-        <v>-477300000</v>
+        <v>296000000</v>
       </c>
       <c r="QF32" s="4">
         <v>0</v>
@@ -17919,7 +17919,7 @@
         <v>643485000</v>
       </c>
       <c r="QH32" s="4">
-        <v>477300000</v>
+        <v>-296000000</v>
       </c>
       <c r="QI32" s="4">
         <v>13513706100</v>
@@ -17931,19 +17931,19 @@
         <v>10663336695</v>
       </c>
       <c r="QL32" s="4">
-        <v>11090729100</v>
+        <v>13513706000</v>
       </c>
       <c r="QM32" s="4">
-        <v>427392405</v>
+        <v>2850369305</v>
       </c>
       <c r="QN32" s="4">
-        <v>-85.00571875875856</v>
+        <v>-0.0000035083171965214102</v>
       </c>
       <c r="QO32" s="4">
         <v>1263075924</v>
       </c>
       <c r="QP32" s="4">
-        <v>-2422977000</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="33">
@@ -18011,19 +18011,19 @@
         <v>18071365</v>
       </c>
       <c r="BB33" s="4">
-        <v>20478900</v>
+        <v>16669500</v>
       </c>
       <c r="BC33" s="4">
-        <v>2407535</v>
+        <v>-1401865</v>
       </c>
       <c r="BD33" s="4">
-        <v>75.25844656133376</v>
+        <v>114.4065684657942</v>
       </c>
       <c r="BE33" s="4">
         <v>19176700</v>
       </c>
       <c r="BF33" s="4">
-        <v>7323200</v>
+        <v>11132600</v>
       </c>
       <c r="BG33" s="4">
         <v>14060600</v>
@@ -18035,19 +18035,19 @@
         <v>9139390</v>
       </c>
       <c r="BJ33" s="4">
-        <v>10025000</v>
+        <v>12971600</v>
       </c>
       <c r="BK33" s="4">
-        <v>885610</v>
+        <v>3832210</v>
       </c>
       <c r="BL33" s="4">
-        <v>82.00422253876587</v>
+        <v>22.128704119515323</v>
       </c>
       <c r="BM33" s="4">
         <v>8711800</v>
       </c>
       <c r="BN33" s="4">
-        <v>4035600</v>
+        <v>1089000</v>
       </c>
       <c r="BO33" s="4">
         <v>14551200</v>
@@ -18059,19 +18059,19 @@
         <v>9458280</v>
       </c>
       <c r="BR33" s="4">
-        <v>11403000</v>
+        <v>12868800</v>
       </c>
       <c r="BS33" s="4">
-        <v>1944720</v>
+        <v>3410520</v>
       </c>
       <c r="BT33" s="4">
-        <v>61.81522584293489</v>
+        <v>33.034094389858865</v>
       </c>
       <c r="BU33" s="4">
         <v>1767676</v>
       </c>
       <c r="BV33" s="4">
-        <v>3148200</v>
+        <v>1682400</v>
       </c>
       <c r="CE33" s="4">
         <v>25799000</v>
@@ -18107,10 +18107,10 @@
         <v>64817900</v>
       </c>
       <c r="FB33" s="4">
-        <v>64367000</v>
+        <v>63732400</v>
       </c>
       <c r="FC33" s="4">
-        <v>-450900</v>
+        <v>-1085500</v>
       </c>
       <c r="FD33" s="4">
         <v>0</v>
@@ -18119,7 +18119,7 @@
         <v>2382200</v>
       </c>
       <c r="FF33" s="4">
-        <v>450900</v>
+        <v>1085500</v>
       </c>
       <c r="FG33" s="4">
         <v>657632800</v>
@@ -18131,19 +18131,19 @@
         <v>373557285</v>
       </c>
       <c r="FJ33" s="4">
-        <v>372882900</v>
+        <v>372851300</v>
       </c>
       <c r="FK33" s="4">
-        <v>-674385</v>
+        <v>-705985</v>
       </c>
       <c r="FL33" s="4">
-        <v>100.23739638384532</v>
+        <v>100.24852018661305</v>
       </c>
       <c r="FM33" s="4">
         <v>98324560</v>
       </c>
       <c r="FN33" s="4">
-        <v>284749900</v>
+        <v>284781500</v>
       </c>
       <c r="JW33" s="4">
         <v>253368000</v>
@@ -18203,19 +18203,19 @@
         <v>18071365</v>
       </c>
       <c r="LV33" s="4">
-        <v>20478900</v>
+        <v>16669500</v>
       </c>
       <c r="LW33" s="4">
-        <v>2407535</v>
+        <v>-1401865</v>
       </c>
       <c r="LX33" s="4">
-        <v>75.25844656133376</v>
+        <v>114.4065684657942</v>
       </c>
       <c r="LY33" s="4">
         <v>19176700</v>
       </c>
       <c r="LZ33" s="4">
-        <v>7323200</v>
+        <v>11132600</v>
       </c>
       <c r="MA33" s="4">
         <v>14060600</v>
@@ -18227,19 +18227,19 @@
         <v>9139390</v>
       </c>
       <c r="MD33" s="4">
-        <v>10025000</v>
+        <v>12971600</v>
       </c>
       <c r="ME33" s="4">
-        <v>885610</v>
+        <v>3832210</v>
       </c>
       <c r="MF33" s="4">
-        <v>82.00422253876587</v>
+        <v>22.128704119515323</v>
       </c>
       <c r="MG33" s="4">
         <v>8711800</v>
       </c>
       <c r="MH33" s="4">
-        <v>4035600</v>
+        <v>1089000</v>
       </c>
       <c r="MY33" s="4">
         <v>25799000</v>
@@ -18275,10 +18275,10 @@
         <v>64817900</v>
       </c>
       <c r="QD33" s="4">
-        <v>64367000</v>
+        <v>63732400</v>
       </c>
       <c r="QE33" s="4">
-        <v>-450900</v>
+        <v>-1085500</v>
       </c>
       <c r="QF33" s="4">
         <v>0</v>
@@ -18287,7 +18287,7 @@
         <v>2382200</v>
       </c>
       <c r="QH33" s="4">
-        <v>450900</v>
+        <v>1085500</v>
       </c>
       <c r="QI33" s="4">
         <v>657632800</v>
@@ -18299,19 +18299,19 @@
         <v>373557285</v>
       </c>
       <c r="QL33" s="4">
-        <v>372882900</v>
+        <v>372851300</v>
       </c>
       <c r="QM33" s="4">
-        <v>-674385</v>
+        <v>-705985</v>
       </c>
       <c r="QN33" s="4">
-        <v>-100.23739638384532</v>
+        <v>-100.24852018661305</v>
       </c>
       <c r="QO33" s="4">
         <v>98324560</v>
       </c>
       <c r="QP33" s="4">
-        <v>-284749900</v>
+        <v>-284781500</v>
       </c>
     </row>
     <row r="34">
@@ -18523,10 +18523,10 @@
         <v>1495000000</v>
       </c>
       <c r="JJ34" s="4">
-        <v>1495000000</v>
+        <v>1595000000</v>
       </c>
       <c r="JK34" s="4">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="JL34" s="4">
         <v>0</v>
@@ -18535,7 +18535,7 @@
         <v>1543800000</v>
       </c>
       <c r="JN34" s="4">
-        <v>0</v>
+        <v>-100000000</v>
       </c>
       <c r="JO34" s="4">
         <v>1495000000</v>
@@ -18547,19 +18547,19 @@
         <v>1495000000</v>
       </c>
       <c r="JR34" s="4">
-        <v>1495000000</v>
+        <v>1595000000</v>
       </c>
       <c r="JS34" s="4">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="JT34" s="4">
-        <v>NaN</v>
+        <v>Infinity</v>
       </c>
       <c r="JU34" s="4">
         <v>0</v>
       </c>
       <c r="JV34" s="4">
-        <v>0</v>
+        <v>-100000000</v>
       </c>
       <c r="JW34" s="4">
         <v>138431000</v>
@@ -18691,10 +18691,10 @@
         <v>2732678900</v>
       </c>
       <c r="QD34" s="4">
-        <v>2732678900</v>
+        <v>2832678900</v>
       </c>
       <c r="QE34" s="4">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="QF34" s="4">
         <v>0</v>
@@ -18703,7 +18703,7 @@
         <v>1543967000</v>
       </c>
       <c r="QH34" s="4">
-        <v>0</v>
+        <v>-100000000</v>
       </c>
       <c r="QI34" s="4">
         <v>2957366000</v>
@@ -18715,19 +18715,19 @@
         <v>2846282465</v>
       </c>
       <c r="QL34" s="4">
-        <v>2846282000</v>
+        <v>2946282000</v>
       </c>
       <c r="QM34" s="4">
-        <v>-465</v>
+        <v>99999535</v>
       </c>
       <c r="QN34" s="4">
-        <v>-100.00041860389122</v>
+        <v>-9.978076408893541</v>
       </c>
       <c r="QO34" s="4">
         <v>56656460</v>
       </c>
       <c r="QP34" s="4">
-        <v>-111084000</v>
+        <v>-11084000</v>
       </c>
     </row>
     <row r="35">
@@ -19211,19 +19211,19 @@
         <v>164376160</v>
       </c>
       <c r="BR36" s="4">
-        <v>164348800</v>
+        <v>242210600</v>
       </c>
       <c r="BS36" s="4">
-        <v>-27360</v>
+        <v>77834440</v>
       </c>
       <c r="BT36" s="4">
-        <v>100.03091167756408</v>
+        <v>12.061655238987038</v>
       </c>
       <c r="BU36" s="4">
         <v>139255800</v>
       </c>
       <c r="BV36" s="4">
-        <v>88537600</v>
+        <v>10675800</v>
       </c>
       <c r="CE36" s="4">
         <v>6750000</v>
@@ -19283,19 +19283,19 @@
         <v>627015895</v>
       </c>
       <c r="FJ36" s="4">
-        <v>625513500</v>
+        <v>703375300</v>
       </c>
       <c r="FK36" s="4">
-        <v>-1502395</v>
+        <v>76359405</v>
       </c>
       <c r="FL36" s="4">
-        <v>100.59862001768651</v>
+        <v>69.57506622983145</v>
       </c>
       <c r="FM36" s="4">
         <v>209902000</v>
       </c>
       <c r="FN36" s="4">
-        <v>252478800</v>
+        <v>174617000</v>
       </c>
       <c r="JW36" s="4">
         <v>234274000</v>
@@ -19451,19 +19451,19 @@
         <v>627015895</v>
       </c>
       <c r="QL36" s="4">
-        <v>625513500</v>
+        <v>703375300</v>
       </c>
       <c r="QM36" s="4">
-        <v>-1502395</v>
+        <v>76359405</v>
       </c>
       <c r="QN36" s="4">
-        <v>-100.59862001768651</v>
+        <v>-69.57506622983145</v>
       </c>
       <c r="QO36" s="4">
         <v>209902000</v>
       </c>
       <c r="QP36" s="4">
-        <v>-252478800</v>
+        <v>-174617000</v>
       </c>
     </row>
     <row r="37">
@@ -19803,19 +19803,19 @@
         <v>2045789500</v>
       </c>
       <c r="F38" s="4">
-        <v>2055374000</v>
+        <v>3873667000</v>
       </c>
       <c r="G38" s="4">
-        <v>9584500</v>
+        <v>1827877500</v>
       </c>
       <c r="H38" s="4">
-        <v>99.53150116373165</v>
+        <v>10.651731275382927</v>
       </c>
       <c r="I38" s="4">
         <v>712157916</v>
       </c>
       <c r="J38" s="4">
-        <v>2036205000</v>
+        <v>217912000</v>
       </c>
       <c r="S38" s="4">
         <v>42250000</v>
@@ -19827,19 +19827,19 @@
         <v>21125000</v>
       </c>
       <c r="V38" s="4">
-        <v>15750000</v>
+        <v>78100000</v>
       </c>
       <c r="W38" s="4">
-        <v>-5375000</v>
+        <v>56975000</v>
       </c>
       <c r="X38" s="4">
-        <v>125.44378698224851</v>
+        <v>-169.70414201183434</v>
       </c>
       <c r="Y38" s="4">
         <v>0</v>
       </c>
       <c r="Z38" s="4">
-        <v>26500000</v>
+        <v>-35850000</v>
       </c>
       <c r="AY38" s="4">
         <v>22546900</v>
@@ -19851,19 +19851,19 @@
         <v>14655485</v>
       </c>
       <c r="BB38" s="4">
-        <v>14433500</v>
+        <v>22546900</v>
       </c>
       <c r="BC38" s="4">
-        <v>-221985</v>
+        <v>7891415</v>
       </c>
       <c r="BD38" s="4">
-        <v>102.81299361394632</v>
+        <v>0</v>
       </c>
       <c r="BE38" s="4">
         <v>451000</v>
       </c>
       <c r="BF38" s="4">
-        <v>8113400</v>
+        <v>0</v>
       </c>
       <c r="BG38" s="4">
         <v>11455800</v>
@@ -19875,19 +19875,19 @@
         <v>7446270</v>
       </c>
       <c r="BJ38" s="4">
-        <v>6637800</v>
+        <v>11455800</v>
       </c>
       <c r="BK38" s="4">
-        <v>-808470</v>
+        <v>4009530</v>
       </c>
       <c r="BL38" s="4">
-        <v>120.16370996101789</v>
+        <v>0</v>
       </c>
       <c r="BM38" s="4">
         <v>461300</v>
       </c>
       <c r="BN38" s="4">
-        <v>4818000</v>
+        <v>0</v>
       </c>
       <c r="BO38" s="4">
         <v>6414000</v>
@@ -19899,19 +19899,19 @@
         <v>4169100</v>
       </c>
       <c r="BR38" s="4">
-        <v>4259100</v>
+        <v>6475800</v>
       </c>
       <c r="BS38" s="4">
-        <v>90000</v>
+        <v>2306700</v>
       </c>
       <c r="BT38" s="4">
-        <v>95.99091273553387</v>
+        <v>-2.752906588266738</v>
       </c>
       <c r="BU38" s="4">
         <v>256800</v>
       </c>
       <c r="BV38" s="4">
-        <v>2154900</v>
+        <v>-61800</v>
       </c>
       <c r="CE38" s="4">
         <v>18275000</v>
@@ -19923,19 +19923,19 @@
         <v>11878750</v>
       </c>
       <c r="CH38" s="4">
-        <v>10702000</v>
+        <v>18275000</v>
       </c>
       <c r="CI38" s="4">
-        <v>-1176750</v>
+        <v>6396250</v>
       </c>
       <c r="CJ38" s="4">
-        <v>118.39749853429744</v>
+        <v>0</v>
       </c>
       <c r="CK38" s="4">
         <v>0</v>
       </c>
       <c r="CL38" s="4">
-        <v>7573000</v>
+        <v>0</v>
       </c>
       <c r="EY38" s="4">
         <v>13041807291</v>
@@ -19947,10 +19947,10 @@
         <v>13041807291</v>
       </c>
       <c r="FB38" s="4">
-        <v>13041523391</v>
+        <v>13223807291</v>
       </c>
       <c r="FC38" s="4">
-        <v>-283900</v>
+        <v>182000000</v>
       </c>
       <c r="FD38" s="4">
         <v>0</v>
@@ -19959,7 +19959,7 @@
         <v>4791689805</v>
       </c>
       <c r="FF38" s="4">
-        <v>283900</v>
+        <v>-182000000</v>
       </c>
       <c r="FG38" s="4">
         <v>17234327991</v>
@@ -19971,19 +19971,19 @@
         <v>15146871396</v>
       </c>
       <c r="FJ38" s="4">
-        <v>15148679791</v>
+        <v>17234327791</v>
       </c>
       <c r="FK38" s="4">
-        <v>1808395</v>
+        <v>2087456395</v>
       </c>
       <c r="FL38" s="4">
-        <v>99.91336849808846</v>
+        <v>0.000009581037540088348</v>
       </c>
       <c r="FM38" s="4">
         <v>713327016</v>
       </c>
       <c r="FN38" s="4">
-        <v>2085648200</v>
+        <v>200</v>
       </c>
       <c r="FO38" s="4">
         <v>48400000</v>
@@ -20067,19 +20067,19 @@
         <v>2069989500</v>
       </c>
       <c r="JZ38" s="4">
-        <v>2103774000</v>
+        <v>3922067000</v>
       </c>
       <c r="KA38" s="4">
-        <v>33784500</v>
+        <v>1852077500</v>
       </c>
       <c r="KB38" s="4">
-        <v>98.36789027190717</v>
+        <v>10.527203157310701</v>
       </c>
       <c r="KC38" s="4">
         <v>712157916</v>
       </c>
       <c r="KD38" s="4">
-        <v>2036205000</v>
+        <v>217912000</v>
       </c>
       <c r="KM38" s="4">
         <v>42250000</v>
@@ -20091,19 +20091,19 @@
         <v>21125000</v>
       </c>
       <c r="KP38" s="4">
-        <v>15750000</v>
+        <v>78100000</v>
       </c>
       <c r="KQ38" s="4">
-        <v>-5375000</v>
+        <v>56975000</v>
       </c>
       <c r="KR38" s="4">
-        <v>125.44378698224851</v>
+        <v>-169.70414201183434</v>
       </c>
       <c r="KS38" s="4">
         <v>0</v>
       </c>
       <c r="KT38" s="4">
-        <v>26500000</v>
+        <v>-35850000</v>
       </c>
       <c r="LS38" s="4">
         <v>22546900</v>
@@ -20115,19 +20115,19 @@
         <v>14655485</v>
       </c>
       <c r="LV38" s="4">
-        <v>14433500</v>
+        <v>22546900</v>
       </c>
       <c r="LW38" s="4">
-        <v>-221985</v>
+        <v>7891415</v>
       </c>
       <c r="LX38" s="4">
-        <v>102.81299361394632</v>
+        <v>0</v>
       </c>
       <c r="LY38" s="4">
         <v>451000</v>
       </c>
       <c r="LZ38" s="4">
-        <v>8113400</v>
+        <v>0</v>
       </c>
       <c r="MA38" s="4">
         <v>11455800</v>
@@ -20139,19 +20139,19 @@
         <v>7446270</v>
       </c>
       <c r="MD38" s="4">
-        <v>6637800</v>
+        <v>11455800</v>
       </c>
       <c r="ME38" s="4">
-        <v>-808470</v>
+        <v>4009530</v>
       </c>
       <c r="MF38" s="4">
-        <v>120.16370996101789</v>
+        <v>0</v>
       </c>
       <c r="MG38" s="4">
         <v>461300</v>
       </c>
       <c r="MH38" s="4">
-        <v>4818000</v>
+        <v>0</v>
       </c>
       <c r="MY38" s="4">
         <v>18275000</v>
@@ -20163,19 +20163,19 @@
         <v>11878750</v>
       </c>
       <c r="NB38" s="4">
-        <v>10702000</v>
+        <v>18275000</v>
       </c>
       <c r="NC38" s="4">
-        <v>-1176750</v>
+        <v>6396250</v>
       </c>
       <c r="ND38" s="4">
-        <v>118.39749853429744</v>
+        <v>0</v>
       </c>
       <c r="NE38" s="4">
         <v>0</v>
       </c>
       <c r="NF38" s="4">
-        <v>7573000</v>
+        <v>0</v>
       </c>
       <c r="QA38" s="4">
         <v>13062807291</v>
@@ -20187,10 +20187,10 @@
         <v>13062807291</v>
       </c>
       <c r="QD38" s="4">
-        <v>13062523391</v>
+        <v>13244807291</v>
       </c>
       <c r="QE38" s="4">
-        <v>-283900</v>
+        <v>182000000</v>
       </c>
       <c r="QF38" s="4">
         <v>0</v>
@@ -20199,7 +20199,7 @@
         <v>4791689805</v>
       </c>
       <c r="QH38" s="4">
-        <v>283900</v>
+        <v>-182000000</v>
       </c>
       <c r="QI38" s="4">
         <v>17303727991</v>
@@ -20211,19 +20211,19 @@
         <v>15192071396</v>
       </c>
       <c r="QL38" s="4">
-        <v>15218079791</v>
+        <v>17303727791</v>
       </c>
       <c r="QM38" s="4">
-        <v>26008395</v>
+        <v>2111656395</v>
       </c>
       <c r="QN38" s="4">
-        <v>-98.76834163937531</v>
+        <v>-0.000009471236965023661</v>
       </c>
       <c r="QO38" s="4">
         <v>713327016</v>
       </c>
       <c r="QP38" s="4">
-        <v>-2085648200</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="39">
@@ -20971,19 +20971,19 @@
         <v>197219500</v>
       </c>
       <c r="F40" s="4">
-        <v>170130000</v>
+        <v>287625000</v>
       </c>
       <c r="G40" s="4">
-        <v>-27089500</v>
+        <v>90405500</v>
       </c>
       <c r="H40" s="4">
-        <v>113.7357107182606</v>
+        <v>54.15995882760072</v>
       </c>
       <c r="I40" s="4">
         <v>78504394</v>
       </c>
       <c r="J40" s="4">
-        <v>224309000</v>
+        <v>106814000</v>
       </c>
       <c r="S40" s="4">
         <v>41300000</v>
@@ -21019,19 +21019,19 @@
         <v>3500000</v>
       </c>
       <c r="AD40" s="4">
-        <v>0</v>
+        <v>14000000</v>
       </c>
       <c r="AE40" s="4">
-        <v>-3500000</v>
+        <v>10500000</v>
       </c>
       <c r="AF40" s="4">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="AG40" s="4">
         <v>0</v>
       </c>
       <c r="AH40" s="4">
-        <v>7000000</v>
+        <v>-7000000</v>
       </c>
       <c r="AI40" s="4">
         <v>8176000</v>
@@ -21067,19 +21067,19 @@
         <v>62878270</v>
       </c>
       <c r="BB40" s="4">
-        <v>52446100</v>
+        <v>55841500</v>
       </c>
       <c r="BC40" s="4">
-        <v>-10432170</v>
+        <v>-7036770</v>
       </c>
       <c r="BD40" s="4">
-        <v>130.81196413323713</v>
+        <v>120.78347121009713</v>
       </c>
       <c r="BE40" s="4">
         <v>22000000</v>
       </c>
       <c r="BF40" s="4">
-        <v>44289700</v>
+        <v>40894300</v>
       </c>
       <c r="BG40" s="4">
         <v>48816000</v>
@@ -21091,19 +21091,19 @@
         <v>31730400</v>
       </c>
       <c r="BJ40" s="4">
-        <v>32828900</v>
+        <v>34206400</v>
       </c>
       <c r="BK40" s="4">
-        <v>1098500</v>
+        <v>2476000</v>
       </c>
       <c r="BL40" s="4">
-        <v>93.5706091679543</v>
+        <v>85.50826426932622</v>
       </c>
       <c r="BM40" s="4">
         <v>10252000</v>
       </c>
       <c r="BN40" s="4">
-        <v>15987100</v>
+        <v>14609600</v>
       </c>
       <c r="BO40" s="4">
         <v>105765000</v>
@@ -21115,19 +21115,19 @@
         <v>68747250</v>
       </c>
       <c r="BR40" s="4">
-        <v>42108320</v>
+        <v>44326220</v>
       </c>
       <c r="BS40" s="4">
-        <v>-26638930</v>
+        <v>-24421030</v>
       </c>
       <c r="BT40" s="4">
-        <v>171.96258551640767</v>
+        <v>165.97113546879538</v>
       </c>
       <c r="BU40" s="4">
         <v>3074000</v>
       </c>
       <c r="BV40" s="4">
-        <v>63656680</v>
+        <v>61438780</v>
       </c>
       <c r="CE40" s="4">
         <v>193506000</v>
@@ -21139,19 +21139,19 @@
         <v>125778900</v>
       </c>
       <c r="CH40" s="4">
-        <v>99585000</v>
+        <v>127485000</v>
       </c>
       <c r="CI40" s="4">
-        <v>-26193900</v>
+        <v>1706100</v>
       </c>
       <c r="CJ40" s="4">
-        <v>138.67565568288026</v>
+        <v>97.48091974999667</v>
       </c>
       <c r="CK40" s="4">
         <v>14923000</v>
       </c>
       <c r="CL40" s="4">
-        <v>93921000</v>
+        <v>66021000</v>
       </c>
       <c r="DK40" s="4">
         <v>79140000</v>
@@ -21259,10 +21259,10 @@
         <v>4633415234</v>
       </c>
       <c r="FB40" s="4">
-        <v>5323323633.89</v>
+        <v>5156937633.89</v>
       </c>
       <c r="FC40" s="4">
-        <v>689908399.8900003</v>
+        <v>523522399.89000034</v>
       </c>
       <c r="FD40" s="4">
         <v>0</v>
@@ -21271,7 +21271,7 @@
         <v>1801877669</v>
       </c>
       <c r="FF40" s="4">
-        <v>-689908399.8900003</v>
+        <v>-523522399.89000034</v>
       </c>
       <c r="FG40" s="4">
         <v>5743349034</v>
@@ -21283,19 +21283,19 @@
         <v>5287234954</v>
       </c>
       <c r="FJ40" s="4">
-        <v>5909930253.89</v>
+        <v>5909930053.89</v>
       </c>
       <c r="FK40" s="4">
-        <v>622695299.8900003</v>
+        <v>622695099.8900003</v>
       </c>
       <c r="FL40" s="4">
-        <v>-36.52183240868169</v>
+        <v>-36.521788560002435</v>
       </c>
       <c r="FM40" s="4">
         <v>146945394</v>
       </c>
       <c r="FN40" s="4">
-        <v>-166581219.89000034</v>
+        <v>-166581019.89000034</v>
       </c>
       <c r="FO40" s="4">
         <v>327141000</v>
@@ -21475,19 +21475,19 @@
         <v>360790000</v>
       </c>
       <c r="JZ40" s="4">
-        <v>194964000</v>
+        <v>312459000</v>
       </c>
       <c r="KA40" s="4">
-        <v>-165826000</v>
+        <v>-48331000</v>
       </c>
       <c r="KB40" s="4">
-        <v>145.96191690457053</v>
+        <v>113.3958812605671</v>
       </c>
       <c r="KC40" s="4">
         <v>78504394</v>
       </c>
       <c r="KD40" s="4">
-        <v>526616000</v>
+        <v>409121000</v>
       </c>
       <c r="KM40" s="4">
         <v>89100000</v>
@@ -21523,19 +21523,19 @@
         <v>3500000</v>
       </c>
       <c r="KX40" s="4">
-        <v>0</v>
+        <v>14000000</v>
       </c>
       <c r="KY40" s="4">
-        <v>-3500000</v>
+        <v>10500000</v>
       </c>
       <c r="KZ40" s="4">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="LA40" s="4">
         <v>0</v>
       </c>
       <c r="LB40" s="4">
-        <v>7000000</v>
+        <v>-7000000</v>
       </c>
       <c r="LC40" s="4">
         <v>8176000</v>
@@ -21571,19 +21571,19 @@
         <v>83600790</v>
       </c>
       <c r="LV40" s="4">
-        <v>74060500</v>
+        <v>77455900</v>
       </c>
       <c r="LW40" s="4">
-        <v>-9540290</v>
+        <v>-6144890</v>
       </c>
       <c r="LX40" s="4">
-        <v>121.19319856734778</v>
+        <v>113.65051523009359</v>
       </c>
       <c r="LY40" s="4">
         <v>22000000</v>
       </c>
       <c r="LZ40" s="4">
-        <v>54556100</v>
+        <v>51160700</v>
       </c>
       <c r="MA40" s="4">
         <v>60746000</v>
@@ -21595,19 +21595,19 @@
         <v>39484900</v>
       </c>
       <c r="MD40" s="4">
-        <v>37313900</v>
+        <v>38691400</v>
       </c>
       <c r="ME40" s="4">
-        <v>-2171000</v>
+        <v>-793500</v>
       </c>
       <c r="MF40" s="4">
-        <v>110.21113677091026</v>
+        <v>103.73216813805494</v>
       </c>
       <c r="MG40" s="4">
         <v>10252000</v>
       </c>
       <c r="MH40" s="4">
-        <v>23432100</v>
+        <v>22054600</v>
       </c>
       <c r="MY40" s="4">
         <v>228536000</v>
@@ -21619,19 +21619,19 @@
         <v>148548400</v>
       </c>
       <c r="NB40" s="4">
-        <v>110745000</v>
+        <v>138645000</v>
       </c>
       <c r="NC40" s="4">
-        <v>-37803400</v>
+        <v>-9903400</v>
       </c>
       <c r="ND40" s="4">
-        <v>147.26157554420936</v>
+        <v>112.38116908120759</v>
       </c>
       <c r="NE40" s="4">
         <v>14923000</v>
       </c>
       <c r="NF40" s="4">
-        <v>117791000</v>
+        <v>89891000</v>
       </c>
       <c r="QA40" s="4">
         <v>5717305734</v>
@@ -21643,10 +21643,10 @@
         <v>5717305734</v>
       </c>
       <c r="QD40" s="4">
-        <v>5376713133.89</v>
+        <v>5210327133.89</v>
       </c>
       <c r="QE40" s="4">
-        <v>-340592600.10999966</v>
+        <v>-506978600.10999966</v>
       </c>
       <c r="QF40" s="4">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1801877669</v>
       </c>
       <c r="QH40" s="4">
-        <v>340592600.10999966</v>
+        <v>506978600.10999966</v>
       </c>
       <c r="QI40" s="4">
         <v>7293349034</v>
@@ -21667,19 +21667,19 @@
         <v>6622170174</v>
       </c>
       <c r="QL40" s="4">
-        <v>6062696953.89</v>
+        <v>6062696753.89</v>
       </c>
       <c r="QM40" s="4">
-        <v>-559473220.1099997</v>
+        <v>-559473420.1099997</v>
       </c>
       <c r="QN40" s="4">
-        <v>-183.35680002048926</v>
+        <v>-183.35682981880564</v>
       </c>
       <c r="QO40" s="4">
         <v>146945394</v>
       </c>
       <c r="QP40" s="4">
-        <v>-1230652080.1099997</v>
+        <v>-1230652280.1099997</v>
       </c>
     </row>
     <row r="41">
@@ -21699,19 +21699,19 @@
         <v>421646500</v>
       </c>
       <c r="F41" s="4">
-        <v>675875000</v>
+        <v>551109000</v>
       </c>
       <c r="G41" s="4">
-        <v>254228500</v>
+        <v>129462500</v>
       </c>
       <c r="H41" s="4">
-        <v>39.70577248951432</v>
+        <v>69.29596237606621</v>
       </c>
       <c r="I41" s="4">
         <v>88075600</v>
       </c>
       <c r="J41" s="4">
-        <v>167418000</v>
+        <v>292184000</v>
       </c>
       <c r="S41" s="4">
         <v>83900000</v>
@@ -21723,19 +21723,19 @@
         <v>41950000</v>
       </c>
       <c r="V41" s="4">
-        <v>24800000</v>
+        <v>31800000</v>
       </c>
       <c r="W41" s="4">
-        <v>-17150000</v>
+        <v>-10150000</v>
       </c>
       <c r="X41" s="4">
-        <v>140.88200238379022</v>
+        <v>124.19547079856972</v>
       </c>
       <c r="Y41" s="4">
         <v>31221000</v>
       </c>
       <c r="Z41" s="4">
-        <v>59100000</v>
+        <v>52100000</v>
       </c>
       <c r="AQ41" s="4">
         <v>33120000</v>
@@ -21771,19 +21771,19 @@
         <v>201040775</v>
       </c>
       <c r="BB41" s="4">
-        <v>190545000</v>
+        <v>186028000</v>
       </c>
       <c r="BC41" s="4">
-        <v>-10495775</v>
+        <v>-15012775</v>
       </c>
       <c r="BD41" s="4">
-        <v>109.69562198087854</v>
+        <v>113.86826520995199</v>
       </c>
       <c r="BE41" s="4">
         <v>14957800</v>
       </c>
       <c r="BF41" s="4">
-        <v>118748500</v>
+        <v>123265500</v>
       </c>
       <c r="BG41" s="4">
         <v>138699000</v>
@@ -21795,19 +21795,19 @@
         <v>90154350</v>
       </c>
       <c r="BJ41" s="4">
-        <v>105948300</v>
+        <v>101303300</v>
       </c>
       <c r="BK41" s="4">
-        <v>15793950</v>
+        <v>11148950</v>
       </c>
       <c r="BL41" s="4">
-        <v>67.46510686553513</v>
+        <v>77.03361750470958</v>
       </c>
       <c r="BM41" s="4">
         <v>10513600</v>
       </c>
       <c r="BN41" s="4">
-        <v>32750700</v>
+        <v>37395700</v>
       </c>
       <c r="BO41" s="4">
         <v>162839000</v>
@@ -21819,19 +21819,19 @@
         <v>105845350</v>
       </c>
       <c r="BR41" s="4">
-        <v>149545800</v>
+        <v>126424800</v>
       </c>
       <c r="BS41" s="4">
-        <v>43700450</v>
+        <v>20579450</v>
       </c>
       <c r="BT41" s="4">
-        <v>23.324001884420458</v>
+        <v>63.8916791607486</v>
       </c>
       <c r="BU41" s="4">
         <v>5345200</v>
       </c>
       <c r="BV41" s="4">
-        <v>13293200</v>
+        <v>36414200</v>
       </c>
       <c r="CE41" s="4">
         <v>196718000</v>
@@ -21843,19 +21843,19 @@
         <v>127866700</v>
       </c>
       <c r="CH41" s="4">
-        <v>197855000</v>
+        <v>190598000</v>
       </c>
       <c r="CI41" s="4">
-        <v>69988300</v>
+        <v>62731300</v>
       </c>
       <c r="CJ41" s="4">
-        <v>-1.6513849411703192</v>
+        <v>8.88872105537586</v>
       </c>
       <c r="CK41" s="4">
         <v>29290000</v>
       </c>
       <c r="CL41" s="4">
-        <v>-1137000</v>
+        <v>6120000</v>
       </c>
       <c r="CM41" s="4">
         <v>49000000</v>
@@ -21963,10 +21963,10 @@
         <v>136874751800</v>
       </c>
       <c r="FB41" s="4">
-        <v>134873921800</v>
+        <v>134783281800</v>
       </c>
       <c r="FC41" s="4">
-        <v>-2000830000</v>
+        <v>-2091470000</v>
       </c>
       <c r="FD41" s="4">
         <v>0</v>
@@ -21975,7 +21975,7 @@
         <v>16037753835</v>
       </c>
       <c r="FF41" s="4">
-        <v>2000830000</v>
+        <v>2091470000</v>
       </c>
       <c r="FG41" s="4">
         <v>139129067300</v>
@@ -21987,19 +21987,19 @@
         <v>138158961125</v>
       </c>
       <c r="FJ41" s="4">
-        <v>136722313900</v>
+        <v>136474367900</v>
       </c>
       <c r="FK41" s="4">
-        <v>-1436647225</v>
+        <v>-1684593225</v>
       </c>
       <c r="FL41" s="4">
-        <v>248.09175140030422</v>
+        <v>273.65039708153597</v>
       </c>
       <c r="FM41" s="4">
         <v>199350850</v>
       </c>
       <c r="FN41" s="4">
-        <v>2406753400</v>
+        <v>2654699400</v>
       </c>
       <c r="JW41" s="4">
         <v>843293000</v>
@@ -22011,19 +22011,19 @@
         <v>421646500</v>
       </c>
       <c r="JZ41" s="4">
-        <v>675875000</v>
+        <v>551109000</v>
       </c>
       <c r="KA41" s="4">
-        <v>254228500</v>
+        <v>129462500</v>
       </c>
       <c r="KB41" s="4">
-        <v>39.70577248951432</v>
+        <v>69.29596237606621</v>
       </c>
       <c r="KC41" s="4">
         <v>88075600</v>
       </c>
       <c r="KD41" s="4">
-        <v>167418000</v>
+        <v>292184000</v>
       </c>
       <c r="KM41" s="4">
         <v>83900000</v>
@@ -22035,19 +22035,19 @@
         <v>41950000</v>
       </c>
       <c r="KP41" s="4">
-        <v>24800000</v>
+        <v>31800000</v>
       </c>
       <c r="KQ41" s="4">
-        <v>-17150000</v>
+        <v>-10150000</v>
       </c>
       <c r="KR41" s="4">
-        <v>140.88200238379022</v>
+        <v>124.19547079856972</v>
       </c>
       <c r="KS41" s="4">
         <v>31221000</v>
       </c>
       <c r="KT41" s="4">
-        <v>59100000</v>
+        <v>52100000</v>
       </c>
       <c r="LK41" s="4">
         <v>33120000</v>
@@ -22083,19 +22083,19 @@
         <v>201040775</v>
       </c>
       <c r="LV41" s="4">
-        <v>190545000</v>
+        <v>186028000</v>
       </c>
       <c r="LW41" s="4">
-        <v>-10495775</v>
+        <v>-15012775</v>
       </c>
       <c r="LX41" s="4">
-        <v>109.69562198087854</v>
+        <v>113.86826520995199</v>
       </c>
       <c r="LY41" s="4">
         <v>14957800</v>
       </c>
       <c r="LZ41" s="4">
-        <v>118748500</v>
+        <v>123265500</v>
       </c>
       <c r="MA41" s="4">
         <v>138699000</v>
@@ -22107,19 +22107,19 @@
         <v>90154350</v>
       </c>
       <c r="MD41" s="4">
-        <v>105948300</v>
+        <v>101303300</v>
       </c>
       <c r="ME41" s="4">
-        <v>15793950</v>
+        <v>11148950</v>
       </c>
       <c r="MF41" s="4">
-        <v>67.46510686553513</v>
+        <v>77.03361750470958</v>
       </c>
       <c r="MG41" s="4">
         <v>10513600</v>
       </c>
       <c r="MH41" s="4">
-        <v>32750700</v>
+        <v>37395700</v>
       </c>
       <c r="MY41" s="4">
         <v>196718000</v>
@@ -22131,19 +22131,19 @@
         <v>127866700</v>
       </c>
       <c r="NB41" s="4">
-        <v>197855000</v>
+        <v>190598000</v>
       </c>
       <c r="NC41" s="4">
-        <v>69988300</v>
+        <v>62731300</v>
       </c>
       <c r="ND41" s="4">
-        <v>-1.6513849411703192</v>
+        <v>8.88872105537586</v>
       </c>
       <c r="NE41" s="4">
         <v>29290000</v>
       </c>
       <c r="NF41" s="4">
-        <v>-1137000</v>
+        <v>6120000</v>
       </c>
       <c r="QA41" s="4">
         <v>136874751800</v>
@@ -22155,10 +22155,10 @@
         <v>136874751800</v>
       </c>
       <c r="QD41" s="4">
-        <v>134873921800</v>
+        <v>134783281800</v>
       </c>
       <c r="QE41" s="4">
-        <v>-2000830000</v>
+        <v>-2091470000</v>
       </c>
       <c r="QF41" s="4">
         <v>0</v>
@@ -22167,7 +22167,7 @@
         <v>16037753835</v>
       </c>
       <c r="QH41" s="4">
-        <v>2000830000</v>
+        <v>2091470000</v>
       </c>
       <c r="QI41" s="4">
         <v>139129067300</v>
@@ -22179,19 +22179,19 @@
         <v>138158961125</v>
       </c>
       <c r="QL41" s="4">
-        <v>136722313900</v>
+        <v>136474367900</v>
       </c>
       <c r="QM41" s="4">
-        <v>-1436647225</v>
+        <v>-1684593225</v>
       </c>
       <c r="QN41" s="4">
-        <v>-248.09175140030422</v>
+        <v>-273.65039708153597</v>
       </c>
       <c r="QO41" s="4">
         <v>199350850</v>
       </c>
       <c r="QP41" s="4">
-        <v>-2406753400</v>
+        <v>-2654699400</v>
       </c>
     </row>
     <row r="42">
@@ -22819,19 +22819,19 @@
         <v>165169500</v>
       </c>
       <c r="AL43" s="4">
-        <v>159357000</v>
+        <v>183525000</v>
       </c>
       <c r="AM43" s="4">
-        <v>-5812500</v>
+        <v>18355500</v>
       </c>
       <c r="AN43" s="4">
-        <v>103.51911218475567</v>
+        <v>88.88687076003741</v>
       </c>
       <c r="AO43" s="4">
         <v>61558620</v>
       </c>
       <c r="AP43" s="4">
-        <v>170982000</v>
+        <v>146814000</v>
       </c>
       <c r="AQ43" s="4">
         <v>10028000</v>
@@ -22867,19 +22867,19 @@
         <v>59378475</v>
       </c>
       <c r="BB43" s="4">
-        <v>64795800</v>
+        <v>64876400</v>
       </c>
       <c r="BC43" s="4">
-        <v>5417325</v>
+        <v>5497925</v>
       </c>
       <c r="BD43" s="4">
-        <v>83.05657659855457</v>
+        <v>82.80448909666822</v>
       </c>
       <c r="BE43" s="4">
         <v>44497400</v>
       </c>
       <c r="BF43" s="4">
-        <v>26555700</v>
+        <v>26475100</v>
       </c>
       <c r="BG43" s="4">
         <v>35622400</v>
@@ -23011,10 +23011,10 @@
         <v>4811738853</v>
       </c>
       <c r="FB43" s="4">
-        <v>4810753553</v>
+        <v>4816503553</v>
       </c>
       <c r="FC43" s="4">
-        <v>-985300</v>
+        <v>4764700</v>
       </c>
       <c r="FD43" s="4">
         <v>0</v>
@@ -23023,7 +23023,7 @@
         <v>1860214008</v>
       </c>
       <c r="FF43" s="4">
-        <v>985300</v>
+        <v>-4764700</v>
       </c>
       <c r="FG43" s="4">
         <v>5446407353</v>
@@ -23035,19 +23035,19 @@
         <v>5174722528</v>
       </c>
       <c r="FJ43" s="4">
-        <v>5174660953</v>
+        <v>5204659553</v>
       </c>
       <c r="FK43" s="4">
-        <v>-61575</v>
+        <v>29937025</v>
       </c>
       <c r="FL43" s="4">
-        <v>100.02266412929026</v>
+        <v>88.98097271351097</v>
       </c>
       <c r="FM43" s="4">
         <v>165551120</v>
       </c>
       <c r="FN43" s="4">
-        <v>271746400</v>
+        <v>241747800</v>
       </c>
       <c r="KU43" s="4">
         <v>0</v>
@@ -23083,19 +23083,19 @@
         <v>165169500</v>
       </c>
       <c r="LF43" s="4">
-        <v>159357000</v>
+        <v>183525000</v>
       </c>
       <c r="LG43" s="4">
-        <v>-5812500</v>
+        <v>18355500</v>
       </c>
       <c r="LH43" s="4">
-        <v>103.51911218475567</v>
+        <v>88.88687076003741</v>
       </c>
       <c r="LI43" s="4">
         <v>61558620</v>
       </c>
       <c r="LJ43" s="4">
-        <v>170982000</v>
+        <v>146814000</v>
       </c>
       <c r="LK43" s="4">
         <v>10028000</v>
@@ -23131,19 +23131,19 @@
         <v>59378475</v>
       </c>
       <c r="LV43" s="4">
-        <v>64795800</v>
+        <v>64876400</v>
       </c>
       <c r="LW43" s="4">
-        <v>5417325</v>
+        <v>5497925</v>
       </c>
       <c r="LX43" s="4">
-        <v>83.05657659855457</v>
+        <v>82.80448909666822</v>
       </c>
       <c r="LY43" s="4">
         <v>44497400</v>
       </c>
       <c r="LZ43" s="4">
-        <v>26555700</v>
+        <v>26475100</v>
       </c>
       <c r="MA43" s="4">
         <v>35622400</v>
@@ -23227,10 +23227,10 @@
         <v>4811738853</v>
       </c>
       <c r="QD43" s="4">
-        <v>4810753553</v>
+        <v>4816503553</v>
       </c>
       <c r="QE43" s="4">
-        <v>-985300</v>
+        <v>4764700</v>
       </c>
       <c r="QF43" s="4">
         <v>0</v>
@@ -23239,7 +23239,7 @@
         <v>1860214008</v>
       </c>
       <c r="QH43" s="4">
-        <v>985300</v>
+        <v>-4764700</v>
       </c>
       <c r="QI43" s="4">
         <v>5446407353</v>
@@ -23251,19 +23251,19 @@
         <v>5174722528</v>
       </c>
       <c r="QL43" s="4">
-        <v>5174660953</v>
+        <v>5204659553</v>
       </c>
       <c r="QM43" s="4">
-        <v>-61575</v>
+        <v>29937025</v>
       </c>
       <c r="QN43" s="4">
-        <v>-100.02266412929026</v>
+        <v>-88.98097271351097</v>
       </c>
       <c r="QO43" s="4">
         <v>165551120</v>
       </c>
       <c r="QP43" s="4">
-        <v>-271746400</v>
+        <v>-241747800</v>
       </c>
     </row>
     <row r="44">
@@ -24723,19 +24723,19 @@
         <v>44550000</v>
       </c>
       <c r="V47" s="4">
-        <v>50300000</v>
+        <v>54300000</v>
       </c>
       <c r="W47" s="4">
-        <v>5750000</v>
+        <v>9750000</v>
       </c>
       <c r="X47" s="4">
-        <v>87.09315375982042</v>
+        <v>78.11447811447812</v>
       </c>
       <c r="Y47" s="4">
         <v>35450000</v>
       </c>
       <c r="Z47" s="4">
-        <v>38800000</v>
+        <v>34800000</v>
       </c>
       <c r="AY47" s="4">
         <v>16352700</v>
@@ -24747,19 +24747,19 @@
         <v>10629255</v>
       </c>
       <c r="BB47" s="4">
-        <v>10627600</v>
+        <v>13022700</v>
       </c>
       <c r="BC47" s="4">
-        <v>-1655</v>
+        <v>2393445</v>
       </c>
       <c r="BD47" s="4">
-        <v>100.02891615102443</v>
+        <v>58.1817419403873</v>
       </c>
       <c r="BE47" s="4">
         <v>8823500</v>
       </c>
       <c r="BF47" s="4">
-        <v>5725100</v>
+        <v>3330000</v>
       </c>
       <c r="BG47" s="4">
         <v>19285000</v>
@@ -24771,19 +24771,19 @@
         <v>12535250</v>
       </c>
       <c r="BJ47" s="4">
-        <v>12506600</v>
+        <v>10892000</v>
       </c>
       <c r="BK47" s="4">
-        <v>-28650</v>
+        <v>-1643250</v>
       </c>
       <c r="BL47" s="4">
-        <v>100.4244601651913</v>
+        <v>124.34534612393051</v>
       </c>
       <c r="BM47" s="4">
         <v>7046600</v>
       </c>
       <c r="BN47" s="4">
-        <v>6778400</v>
+        <v>8393000</v>
       </c>
       <c r="BO47" s="4">
         <v>14122000</v>
@@ -24843,19 +24843,19 @@
         <v>5265000</v>
       </c>
       <c r="CX47" s="4">
-        <v>5260000</v>
+        <v>4200000</v>
       </c>
       <c r="CY47" s="4">
-        <v>-5000</v>
+        <v>-1065000</v>
       </c>
       <c r="CZ47" s="4">
-        <v>100.1763668430335</v>
+        <v>137.56613756613757</v>
       </c>
       <c r="DA47" s="4">
         <v>0</v>
       </c>
       <c r="DB47" s="4">
-        <v>2840000</v>
+        <v>3900000</v>
       </c>
       <c r="EY47" s="4">
         <v>1282531823</v>
@@ -24867,10 +24867,10 @@
         <v>1282531823</v>
       </c>
       <c r="FB47" s="4">
-        <v>1277551823</v>
+        <v>1276751823</v>
       </c>
       <c r="FC47" s="4">
-        <v>-4980000</v>
+        <v>-5780000</v>
       </c>
       <c r="FD47" s="4">
         <v>0</v>
@@ -24879,7 +24879,7 @@
         <v>562647870</v>
       </c>
       <c r="FF47" s="4">
-        <v>4980000</v>
+        <v>5780000</v>
       </c>
       <c r="FG47" s="4">
         <v>1452930523</v>
@@ -24891,19 +24891,19 @@
         <v>1378159578</v>
       </c>
       <c r="FJ47" s="4">
-        <v>1378128423</v>
+        <v>1381048923</v>
       </c>
       <c r="FK47" s="4">
-        <v>-31155</v>
+        <v>2889345</v>
       </c>
       <c r="FL47" s="4">
-        <v>100.04166725457328</v>
+        <v>96.1357382871114</v>
       </c>
       <c r="FM47" s="4">
         <v>60556100</v>
       </c>
       <c r="FN47" s="4">
-        <v>74802100</v>
+        <v>71881600</v>
       </c>
       <c r="JW47" s="4">
         <v>11776000</v>
@@ -24939,19 +24939,19 @@
         <v>44550000</v>
       </c>
       <c r="KP47" s="4">
-        <v>50300000</v>
+        <v>54300000</v>
       </c>
       <c r="KQ47" s="4">
-        <v>5750000</v>
+        <v>9750000</v>
       </c>
       <c r="KR47" s="4">
-        <v>87.09315375982042</v>
+        <v>78.11447811447812</v>
       </c>
       <c r="KS47" s="4">
         <v>35450000</v>
       </c>
       <c r="KT47" s="4">
-        <v>38800000</v>
+        <v>34800000</v>
       </c>
       <c r="LS47" s="4">
         <v>16352700</v>
@@ -24963,19 +24963,19 @@
         <v>10629255</v>
       </c>
       <c r="LV47" s="4">
-        <v>10627600</v>
+        <v>13022700</v>
       </c>
       <c r="LW47" s="4">
-        <v>-1655</v>
+        <v>2393445</v>
       </c>
       <c r="LX47" s="4">
-        <v>100.02891615102443</v>
+        <v>58.1817419403873</v>
       </c>
       <c r="LY47" s="4">
         <v>8823500</v>
       </c>
       <c r="LZ47" s="4">
-        <v>5725100</v>
+        <v>3330000</v>
       </c>
       <c r="MA47" s="4">
         <v>19285000</v>
@@ -24987,19 +24987,19 @@
         <v>12535250</v>
       </c>
       <c r="MD47" s="4">
-        <v>12506600</v>
+        <v>10892000</v>
       </c>
       <c r="ME47" s="4">
-        <v>-28650</v>
+        <v>-1643250</v>
       </c>
       <c r="MF47" s="4">
-        <v>100.4244601651913</v>
+        <v>124.34534612393051</v>
       </c>
       <c r="MG47" s="4">
         <v>7046600</v>
       </c>
       <c r="MH47" s="4">
-        <v>6778400</v>
+        <v>8393000</v>
       </c>
       <c r="MY47" s="4">
         <v>11663000</v>
@@ -25035,19 +25035,19 @@
         <v>5265000</v>
       </c>
       <c r="NR47" s="4">
-        <v>5260000</v>
+        <v>4200000</v>
       </c>
       <c r="NS47" s="4">
-        <v>-5000</v>
+        <v>-1065000</v>
       </c>
       <c r="NT47" s="4">
-        <v>100.1763668430335</v>
+        <v>137.56613756613757</v>
       </c>
       <c r="NU47" s="4">
         <v>0</v>
       </c>
       <c r="NV47" s="4">
-        <v>2840000</v>
+        <v>3900000</v>
       </c>
       <c r="QA47" s="4">
         <v>1282531823</v>
@@ -25059,10 +25059,10 @@
         <v>1282531823</v>
       </c>
       <c r="QD47" s="4">
-        <v>1277551823</v>
+        <v>1276751823</v>
       </c>
       <c r="QE47" s="4">
-        <v>-4980000</v>
+        <v>-5780000</v>
       </c>
       <c r="QF47" s="4">
         <v>0</v>
@@ -25071,7 +25071,7 @@
         <v>562647870</v>
       </c>
       <c r="QH47" s="4">
-        <v>4980000</v>
+        <v>5780000</v>
       </c>
       <c r="QI47" s="4">
         <v>1452930523</v>
@@ -25083,19 +25083,19 @@
         <v>1378159578</v>
       </c>
       <c r="QL47" s="4">
-        <v>1378128423</v>
+        <v>1381048923</v>
       </c>
       <c r="QM47" s="4">
-        <v>-31155</v>
+        <v>2889345</v>
       </c>
       <c r="QN47" s="4">
-        <v>-100.04166725457328</v>
+        <v>-96.1357382871114</v>
       </c>
       <c r="QO47" s="4">
         <v>60556100</v>
       </c>
       <c r="QP47" s="4">
-        <v>-74802100</v>
+        <v>-71881600</v>
       </c>
     </row>
     <row r="48">
@@ -25115,19 +25115,19 @@
         <v>53800000</v>
       </c>
       <c r="V48" s="4">
-        <v>55850000</v>
+        <v>55800000</v>
       </c>
       <c r="W48" s="4">
-        <v>2050000</v>
+        <v>2000000</v>
       </c>
       <c r="X48" s="4">
-        <v>96.18959107806691</v>
+        <v>96.28252788104089</v>
       </c>
       <c r="Y48" s="4">
         <v>24150000</v>
       </c>
       <c r="Z48" s="4">
-        <v>51750000</v>
+        <v>51800000</v>
       </c>
       <c r="AY48" s="4">
         <v>25409800</v>
@@ -25355,19 +25355,19 @@
         <v>2094140666</v>
       </c>
       <c r="FJ48" s="4">
-        <v>2094254016</v>
+        <v>2094204016</v>
       </c>
       <c r="FK48" s="4">
-        <v>113350</v>
+        <v>63350</v>
       </c>
       <c r="FL48" s="4">
-        <v>99.89010078586907</v>
+        <v>99.93857860418885</v>
       </c>
       <c r="FM48" s="4">
         <v>51585500</v>
       </c>
       <c r="FN48" s="4">
-        <v>103026605</v>
+        <v>103076605</v>
       </c>
       <c r="KM48" s="4">
         <v>107600000</v>
@@ -25379,19 +25379,19 @@
         <v>53800000</v>
       </c>
       <c r="KP48" s="4">
-        <v>55850000</v>
+        <v>55800000</v>
       </c>
       <c r="KQ48" s="4">
-        <v>2050000</v>
+        <v>2000000</v>
       </c>
       <c r="KR48" s="4">
-        <v>96.18959107806691</v>
+        <v>96.28252788104089</v>
       </c>
       <c r="KS48" s="4">
         <v>24150000</v>
       </c>
       <c r="KT48" s="4">
-        <v>51750000</v>
+        <v>51800000</v>
       </c>
       <c r="LS48" s="4">
         <v>25409800</v>
@@ -25499,19 +25499,19 @@
         <v>2094140666</v>
       </c>
       <c r="QL48" s="4">
-        <v>2094254016</v>
+        <v>2094204016</v>
       </c>
       <c r="QM48" s="4">
-        <v>113350</v>
+        <v>63350</v>
       </c>
       <c r="QN48" s="4">
-        <v>-99.89010078586907</v>
+        <v>-99.93857860418885</v>
       </c>
       <c r="QO48" s="4">
         <v>51585500</v>
       </c>
       <c r="QP48" s="4">
-        <v>-103026605</v>
+        <v>-103076605</v>
       </c>
     </row>
     <row r="49">
@@ -26483,19 +26483,19 @@
         <v>17911530</v>
       </c>
       <c r="BB51" s="4">
-        <v>12256200</v>
+        <v>12922200</v>
       </c>
       <c r="BC51" s="4">
-        <v>-5655330</v>
+        <v>-4989330</v>
       </c>
       <c r="BD51" s="4">
-        <v>158.6368429401939</v>
+        <v>151.7314744827972</v>
       </c>
       <c r="BE51" s="4">
         <v>6715700</v>
       </c>
       <c r="BF51" s="4">
-        <v>15300000</v>
+        <v>14634000</v>
       </c>
       <c r="BG51" s="4">
         <v>9616500</v>
@@ -26675,19 +26675,19 @@
         <v>1335134106</v>
       </c>
       <c r="FJ51" s="4">
-        <v>1331856056</v>
+        <v>1332522056</v>
       </c>
       <c r="FK51" s="4">
-        <v>-3278050</v>
+        <v>-2612050</v>
       </c>
       <c r="FL51" s="4">
-        <v>103.29960798879479</v>
+        <v>102.62922806154006</v>
       </c>
       <c r="FM51" s="4">
         <v>16270700</v>
       </c>
       <c r="FN51" s="4">
-        <v>102624700</v>
+        <v>101958700</v>
       </c>
       <c r="KM51" s="4">
         <v>96550000</v>
@@ -26723,19 +26723,19 @@
         <v>17911530</v>
       </c>
       <c r="LV51" s="4">
-        <v>12256200</v>
+        <v>12922200</v>
       </c>
       <c r="LW51" s="4">
-        <v>-5655330</v>
+        <v>-4989330</v>
       </c>
       <c r="LX51" s="4">
-        <v>158.6368429401939</v>
+        <v>151.7314744827972</v>
       </c>
       <c r="LY51" s="4">
         <v>6715700</v>
       </c>
       <c r="LZ51" s="4">
-        <v>15300000</v>
+        <v>14634000</v>
       </c>
       <c r="MA51" s="4">
         <v>9616500</v>
@@ -26819,19 +26819,19 @@
         <v>1335134106</v>
       </c>
       <c r="QL51" s="4">
-        <v>1331856056</v>
+        <v>1332522056</v>
       </c>
       <c r="QM51" s="4">
-        <v>-3278050</v>
+        <v>-2612050</v>
       </c>
       <c r="QN51" s="4">
-        <v>-103.29960798879479</v>
+        <v>-102.62922806154006</v>
       </c>
       <c r="QO51" s="4">
         <v>16270700</v>
       </c>
       <c r="QP51" s="4">
-        <v>-102624700</v>
+        <v>-101958700</v>
       </c>
     </row>
     <row r="52">
@@ -27387,19 +27387,19 @@
         <v>14880320</v>
       </c>
       <c r="BB53" s="4">
-        <v>13174800</v>
+        <v>13393700</v>
       </c>
       <c r="BC53" s="4">
-        <v>-1705520</v>
+        <v>-1486620</v>
       </c>
       <c r="BD53" s="4">
-        <v>121.2857941611087</v>
+        <v>118.55380606254245</v>
       </c>
       <c r="BE53" s="4">
         <v>1880800</v>
       </c>
       <c r="BF53" s="4">
-        <v>9718000</v>
+        <v>9499100</v>
       </c>
       <c r="BG53" s="4">
         <v>5157400</v>
@@ -27411,19 +27411,19 @@
         <v>3352310</v>
       </c>
       <c r="BJ53" s="4">
-        <v>3741500</v>
+        <v>3453200</v>
       </c>
       <c r="BK53" s="4">
-        <v>389190</v>
+        <v>100890</v>
       </c>
       <c r="BL53" s="4">
-        <v>78.4393021954584</v>
+        <v>94.41080500141267</v>
       </c>
       <c r="BM53" s="4">
         <v>0</v>
       </c>
       <c r="BN53" s="4">
-        <v>1415900</v>
+        <v>1704200</v>
       </c>
       <c r="BO53" s="4">
         <v>9117600</v>
@@ -27435,19 +27435,19 @@
         <v>5926440</v>
       </c>
       <c r="BR53" s="4">
-        <v>5520000</v>
+        <v>5589000</v>
       </c>
       <c r="BS53" s="4">
-        <v>-406440</v>
+        <v>-337440</v>
       </c>
       <c r="BT53" s="4">
-        <v>112.73643440003008</v>
+        <v>110.57421125860189</v>
       </c>
       <c r="BU53" s="4">
         <v>85800</v>
       </c>
       <c r="BV53" s="4">
-        <v>3597600</v>
+        <v>3528600</v>
       </c>
       <c r="CE53" s="4">
         <v>7688000</v>
@@ -27531,19 +27531,19 @@
         <v>1120643415</v>
       </c>
       <c r="FJ53" s="4">
-        <v>1115715615</v>
+        <v>1115715215</v>
       </c>
       <c r="FK53" s="4">
-        <v>-4927800</v>
+        <v>-4928200</v>
       </c>
       <c r="FL53" s="4">
-        <v>105.42708055709129</v>
+        <v>105.42752108475533</v>
       </c>
       <c r="FM53" s="4">
         <v>13966600</v>
       </c>
       <c r="FN53" s="4">
-        <v>95728000</v>
+        <v>95728400</v>
       </c>
       <c r="KM53" s="4">
         <v>108750000</v>
@@ -27579,19 +27579,19 @@
         <v>14880320</v>
       </c>
       <c r="LV53" s="4">
-        <v>13174800</v>
+        <v>13393700</v>
       </c>
       <c r="LW53" s="4">
-        <v>-1705520</v>
+        <v>-1486620</v>
       </c>
       <c r="LX53" s="4">
-        <v>121.2857941611087</v>
+        <v>118.55380606254245</v>
       </c>
       <c r="LY53" s="4">
         <v>1880800</v>
       </c>
       <c r="LZ53" s="4">
-        <v>9718000</v>
+        <v>9499100</v>
       </c>
       <c r="MA53" s="4">
         <v>5157400</v>
@@ -27603,19 +27603,19 @@
         <v>3352310</v>
       </c>
       <c r="MD53" s="4">
-        <v>3741500</v>
+        <v>3453200</v>
       </c>
       <c r="ME53" s="4">
-        <v>389190</v>
+        <v>100890</v>
       </c>
       <c r="MF53" s="4">
-        <v>78.4393021954584</v>
+        <v>94.41080500141267</v>
       </c>
       <c r="MG53" s="4">
         <v>0</v>
       </c>
       <c r="MH53" s="4">
-        <v>1415900</v>
+        <v>1704200</v>
       </c>
       <c r="MY53" s="4">
         <v>7688000</v>
@@ -27675,19 +27675,19 @@
         <v>1120643415</v>
       </c>
       <c r="QL53" s="4">
-        <v>1115715615</v>
+        <v>1115715215</v>
       </c>
       <c r="QM53" s="4">
-        <v>-4927800</v>
+        <v>-4928200</v>
       </c>
       <c r="QN53" s="4">
-        <v>-105.42708055709129</v>
+        <v>-105.42752108475533</v>
       </c>
       <c r="QO53" s="4">
         <v>13966600</v>
       </c>
       <c r="QP53" s="4">
-        <v>-95728000</v>
+        <v>-95728400</v>
       </c>
     </row>
     <row r="54">
@@ -28243,19 +28243,19 @@
         <v>121747000</v>
       </c>
       <c r="F55" s="4">
-        <v>138814000</v>
+        <v>143776000</v>
       </c>
       <c r="G55" s="4">
-        <v>17067000</v>
+        <v>22029000</v>
       </c>
       <c r="H55" s="4">
-        <v>85.98158476184217</v>
+        <v>81.905919653051</v>
       </c>
       <c r="I55" s="4">
         <v>34441600</v>
       </c>
       <c r="J55" s="4">
-        <v>104680000</v>
+        <v>99718000</v>
       </c>
       <c r="S55" s="4">
         <v>138000000</v>
@@ -28267,19 +28267,19 @@
         <v>69000000</v>
       </c>
       <c r="V55" s="4">
-        <v>93000000</v>
+        <v>132000000</v>
       </c>
       <c r="W55" s="4">
-        <v>24000000</v>
+        <v>63000000</v>
       </c>
       <c r="X55" s="4">
-        <v>65.21739130434783</v>
+        <v>8.695652173913043</v>
       </c>
       <c r="Y55" s="4">
         <v>22800000</v>
       </c>
       <c r="Z55" s="4">
-        <v>45000000</v>
+        <v>6000000</v>
       </c>
       <c r="AI55" s="4">
         <v>170481000</v>
@@ -28315,19 +28315,19 @@
         <v>33627230</v>
       </c>
       <c r="BB55" s="4">
-        <v>33142600</v>
+        <v>33155600</v>
       </c>
       <c r="BC55" s="4">
-        <v>-484630</v>
+        <v>-471630</v>
       </c>
       <c r="BD55" s="4">
-        <v>102.67648314433613</v>
+        <v>102.60468758715567</v>
       </c>
       <c r="BE55" s="4">
         <v>10738700</v>
       </c>
       <c r="BF55" s="4">
-        <v>18591600</v>
+        <v>18578600</v>
       </c>
       <c r="BG55" s="4">
         <v>15498600</v>
@@ -28363,19 +28363,19 @@
         <v>22614410</v>
       </c>
       <c r="BR55" s="4">
-        <v>24813200</v>
+        <v>24816200</v>
       </c>
       <c r="BS55" s="4">
-        <v>2198790</v>
+        <v>2201790</v>
       </c>
       <c r="BT55" s="4">
-        <v>81.94307460218</v>
+        <v>81.91843797194545</v>
       </c>
       <c r="BU55" s="4">
         <v>5443400</v>
       </c>
       <c r="BV55" s="4">
-        <v>9978200</v>
+        <v>9975200</v>
       </c>
       <c r="BW55" s="4">
         <v>4620000</v>
@@ -28387,19 +28387,19 @@
         <v>3003000</v>
       </c>
       <c r="BZ55" s="4">
-        <v>4620000</v>
+        <v>6351800</v>
       </c>
       <c r="CA55" s="4">
-        <v>1617000</v>
+        <v>3348800</v>
       </c>
       <c r="CB55" s="4">
-        <v>0</v>
+        <v>-107.0995670995671</v>
       </c>
       <c r="CC55" s="4">
         <v>0</v>
       </c>
       <c r="CD55" s="4">
-        <v>0</v>
+        <v>-1731800</v>
       </c>
       <c r="CE55" s="4">
         <v>104562000</v>
@@ -28411,19 +28411,19 @@
         <v>67965300</v>
       </c>
       <c r="CH55" s="4">
-        <v>44212000</v>
+        <v>83482000</v>
       </c>
       <c r="CI55" s="4">
-        <v>-23753300</v>
+        <v>15516700</v>
       </c>
       <c r="CJ55" s="4">
-        <v>164.90557891831776</v>
+        <v>57.60082193203212</v>
       </c>
       <c r="CK55" s="4">
         <v>4650000</v>
       </c>
       <c r="CL55" s="4">
-        <v>60350000</v>
+        <v>21080000</v>
       </c>
       <c r="DK55" s="4">
         <v>39140000</v>
@@ -28483,10 +28483,10 @@
         <v>3915686570</v>
       </c>
       <c r="FB55" s="4">
-        <v>3884392570</v>
+        <v>4259316730</v>
       </c>
       <c r="FC55" s="4">
-        <v>-31294000</v>
+        <v>343630160</v>
       </c>
       <c r="FD55" s="4">
         <v>0</v>
@@ -28495,7 +28495,7 @@
         <v>2153992241</v>
       </c>
       <c r="FF55" s="4">
-        <v>31294000</v>
+        <v>-343630160</v>
       </c>
       <c r="FG55" s="4">
         <v>4734955270</v>
@@ -28507,19 +28507,19 @@
         <v>4359483350</v>
       </c>
       <c r="FJ55" s="4">
-        <v>4363235670</v>
+        <v>4823139630</v>
       </c>
       <c r="FK55" s="4">
-        <v>3752320</v>
+        <v>463656280</v>
       </c>
       <c r="FL55" s="4">
-        <v>99.00063898253696</v>
+        <v>-23.48627295484573</v>
       </c>
       <c r="FM55" s="4">
         <v>142422704</v>
       </c>
       <c r="FN55" s="4">
-        <v>371719600</v>
+        <v>-88184360</v>
       </c>
       <c r="JW55" s="4">
         <v>243494000</v>
@@ -28531,19 +28531,19 @@
         <v>121747000</v>
       </c>
       <c r="JZ55" s="4">
-        <v>138814000</v>
+        <v>143776000</v>
       </c>
       <c r="KA55" s="4">
-        <v>17067000</v>
+        <v>22029000</v>
       </c>
       <c r="KB55" s="4">
-        <v>85.98158476184217</v>
+        <v>81.905919653051</v>
       </c>
       <c r="KC55" s="4">
         <v>34441600</v>
       </c>
       <c r="KD55" s="4">
-        <v>104680000</v>
+        <v>99718000</v>
       </c>
       <c r="KM55" s="4">
         <v>138000000</v>
@@ -28555,19 +28555,19 @@
         <v>69000000</v>
       </c>
       <c r="KP55" s="4">
-        <v>93000000</v>
+        <v>132000000</v>
       </c>
       <c r="KQ55" s="4">
-        <v>24000000</v>
+        <v>63000000</v>
       </c>
       <c r="KR55" s="4">
-        <v>65.21739130434783</v>
+        <v>8.695652173913043</v>
       </c>
       <c r="KS55" s="4">
         <v>22800000</v>
       </c>
       <c r="KT55" s="4">
-        <v>45000000</v>
+        <v>6000000</v>
       </c>
       <c r="LC55" s="4">
         <v>170481000</v>
@@ -28603,19 +28603,19 @@
         <v>33627230</v>
       </c>
       <c r="LV55" s="4">
-        <v>33142600</v>
+        <v>33155600</v>
       </c>
       <c r="LW55" s="4">
-        <v>-484630</v>
+        <v>-471630</v>
       </c>
       <c r="LX55" s="4">
-        <v>102.67648314433613</v>
+        <v>102.60468758715567</v>
       </c>
       <c r="LY55" s="4">
         <v>10738700</v>
       </c>
       <c r="LZ55" s="4">
-        <v>18591600</v>
+        <v>18578600</v>
       </c>
       <c r="MA55" s="4">
         <v>15498600</v>
@@ -28651,19 +28651,19 @@
         <v>3003000</v>
       </c>
       <c r="MT55" s="4">
-        <v>4620000</v>
+        <v>6351800</v>
       </c>
       <c r="MU55" s="4">
-        <v>1617000</v>
+        <v>3348800</v>
       </c>
       <c r="MV55" s="4">
-        <v>0</v>
+        <v>-107.0995670995671</v>
       </c>
       <c r="MW55" s="4">
         <v>0</v>
       </c>
       <c r="MX55" s="4">
-        <v>0</v>
+        <v>-1731800</v>
       </c>
       <c r="MY55" s="4">
         <v>104562000</v>
@@ -28675,19 +28675,19 @@
         <v>67965300</v>
       </c>
       <c r="NB55" s="4">
-        <v>44212000</v>
+        <v>83482000</v>
       </c>
       <c r="NC55" s="4">
-        <v>-23753300</v>
+        <v>15516700</v>
       </c>
       <c r="ND55" s="4">
-        <v>164.90557891831776</v>
+        <v>57.60082193203212</v>
       </c>
       <c r="NE55" s="4">
         <v>4650000</v>
       </c>
       <c r="NF55" s="4">
-        <v>60350000</v>
+        <v>21080000</v>
       </c>
       <c r="QA55" s="4">
         <v>3915686570</v>
@@ -28699,10 +28699,10 @@
         <v>3915686570</v>
       </c>
       <c r="QD55" s="4">
-        <v>3884392570</v>
+        <v>4259316730</v>
       </c>
       <c r="QE55" s="4">
-        <v>-31294000</v>
+        <v>343630160</v>
       </c>
       <c r="QF55" s="4">
         <v>0</v>
@@ -28711,7 +28711,7 @@
         <v>2153992241</v>
       </c>
       <c r="QH55" s="4">
-        <v>31294000</v>
+        <v>-343630160</v>
       </c>
       <c r="QI55" s="4">
         <v>4734955270</v>
@@ -28723,19 +28723,19 @@
         <v>4359483350</v>
       </c>
       <c r="QL55" s="4">
-        <v>4363235670</v>
+        <v>4823139630</v>
       </c>
       <c r="QM55" s="4">
-        <v>3752320</v>
+        <v>463656280</v>
       </c>
       <c r="QN55" s="4">
-        <v>-99.00063898253696</v>
+        <v>23.48627295484573</v>
       </c>
       <c r="QO55" s="4">
         <v>142422704</v>
       </c>
       <c r="QP55" s="4">
-        <v>-371719600</v>
+        <v>88184360</v>
       </c>
     </row>
   </sheetData>
